--- a/網站盤點表-英文.xlsx
+++ b/網站盤點表-英文.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
+  <workbookPr codeName="ThisWorkbook"/>
   <sheets>
-    <sheet name="英文" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
 </workbook>
 </file>
@@ -398,14 +398,6 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:F71"/>
-  <cols>
-    <col min="1" max="1" width="80.83203125" customWidth="1"/>
-    <col min="2" max="2" width="60.83203125" customWidth="1"/>
-    <col min="3" max="3" width="50.83203125" customWidth="1"/>
-    <col min="4" max="4" width="60.83203125" customWidth="1"/>
-    <col min="5" max="5" width="12.83203125" customWidth="1"/>
-    <col min="6" max="6" width="50.83203125" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -475,10 +467,10 @@
         <v>https://foreigntalentact.ndc.gov.tw/en/Content_List.aspx?n=6501F7D3D7CCA8A0</v>
       </c>
       <c r="C4" t="str">
-        <v>建議與中文版同步檢查譯文準確性與法規連結一致性。</v>
+        <v>【建議修正】相關檔案「111年外國專業人才延攬及僱用相關法規彙編」標示(待更新)，已歷時約4年未更新，建議儘速更新為最新版本（含115年1月1日施行之修正條文）。</v>
       </c>
       <c r="D4" t="str">
-        <v>已檢視英文版公開頁面；建議與中文版同步檢查譯文與法規說明是否一致。</v>
+        <v>頁面說明外國人才專法立法沿革、修法重點，內文已涵蓋2025年第二次修法內容，內容正確。惟相關檔案「111年法規彙編」仍標示待更新，應更新為最新彙編版本。</v>
       </c>
       <c r="E4" t="str">
         <v>每半年</v>
@@ -638,7 +630,7 @@
         <v>建議與中文版同步檢查譯文準確性與法規連結一致性。</v>
       </c>
       <c r="D12" t="str">
-        <v>已檢視英文版公開頁面；建議與中文版同步檢查譯文與法規說明是否一致。</v>
+        <v>說明2025修法後放寬至前1,500大畢業生可免2年工作經驗之規定。</v>
       </c>
       <c r="E12" t="str">
         <v>每年</v>
@@ -695,7 +687,7 @@
         <v>https://foreigntalentact.ndc.gov.tw/en/Content_List.aspx?n=21B65CD3BBA62A7F</v>
       </c>
       <c r="C15" t="str">
-        <v>建議與中文版同步檢查譯文準確性與法規連結一致性。</v>
+        <v>【建議定期確認】收費標準如有調整，應及時更新。</v>
       </c>
       <c r="D15" t="str">
         <v>已檢視英文版公開頁面；建議與中文版同步檢查譯文與法規說明是否一致。</v>
@@ -1015,10 +1007,10 @@
         <v>https://foreigntalentact.ndc.gov.tw/en/Content_List.aspx?n=24C15F2CEE245632</v>
       </c>
       <c r="C31" t="str">
-        <v>建議與中文版同步檢查譯文準確性與法規連結一致性。</v>
+        <v>【建議修正】相關檔案「就業金卡申辦流程」PDF顯示日期為20211019，已超過4年未更新，應更新至現行版本（含115年修法後之申辦方式）。</v>
       </c>
       <c r="D31" t="str">
-        <v>已檢視英文版公開頁面；建議與中文版同步檢查譯文與法規說明是否一致。</v>
+        <v>就業金卡頁面說明申辦方式，並連結至就業金卡官方網站及申辦窗口平台，惟所附申辦流程PDF日期偏舊，需更新。</v>
       </c>
       <c r="E31" t="str">
         <v>每季</v>
@@ -1155,10 +1147,10 @@
         <v>https://foreigntalentact.ndc.gov.tw/en/Content_List.aspx?n=9436F694D1508C97</v>
       </c>
       <c r="C38" t="str">
-        <v>建議與中文版同步檢查譯文準確性與法規連結一致性。</v>
+        <v>【建議確認】修法後應確認Q&amp;A各子項是否已更新至115年修法內容。</v>
       </c>
       <c r="D38" t="str">
-        <v>已檢視英文版公開頁面；建議與中文版同步檢查譯文與法規說明是否一致。</v>
+        <v>頁面分為「關於本法」及「工作/尋職/數位遊牧」等多個分類，內含多個子頁面。2025修法後應定期確認各Q&amp;A內容是否與現行規定一致。</v>
       </c>
       <c r="E38" t="str">
         <v>每半年</v>

--- a/網站盤點表-英文.xlsx
+++ b/網站盤點表-英文.xlsx
@@ -427,10 +427,10 @@
         <v>https://foreigntalentact.ndc.gov.tw/en/Default.aspx</v>
       </c>
       <c r="C2" t="str">
-        <v>建議與中文版同步檢查譯文準確性與法規連結一致性。</v>
+        <v>【建議檢視】建議檢視法規內容是否導向最新版本（含115年1月1日施行之條文）。</v>
       </c>
       <c r="D2" t="str">
-        <v>已檢視英文版公開頁面；建議與中文版同步檢查譯文與法規說明是否一致。</v>
+        <v>頁面說明法規內容，建議確認相關連結皆已更新至最新修法版本。</v>
       </c>
       <c r="E2" t="str">
         <v>每季</v>
@@ -447,10 +447,10 @@
         <v>https://foreigntalentact.ndc.gov.tw/en/News.aspx?n=8745CCDE1FD96144&amp;sms=843D002B5C4B741F</v>
       </c>
       <c r="C3" t="str">
-        <v>建議與中文版同步檢查譯文準確性與法規連結一致性。</v>
+        <v>【建議檢視】建議檢視法規內容是否導向最新版本（含115年1月1日施行之條文）。</v>
       </c>
       <c r="D3" t="str">
-        <v>已檢視英文版公開頁面；建議與中文版同步檢查譯文與法規說明是否一致。</v>
+        <v>頁面說明法規內容，建議確認相關連結皆已更新至最新修法版本。</v>
       </c>
       <c r="E3" t="str">
         <v>每月</v>
@@ -487,10 +487,10 @@
         <v>https://foreigntalentact.ndc.gov.tw/en/Content_List.aspx?n=21F0223770A20817</v>
       </c>
       <c r="C5" t="str">
-        <v>建議與中文版同步檢查譯文準確性與法規連結一致性。</v>
+        <v>【建議檢視】建議檢視法規內容是否導向最新版本（含115年1月1日施行之條文）。</v>
       </c>
       <c r="D5" t="str">
-        <v>已檢視英文版公開頁面；建議與中文版同步檢查譯文與法規說明是否一致。</v>
+        <v>頁面說明法規內容，建議確認相關連結皆已更新至最新修法版本。</v>
       </c>
       <c r="E5" t="str">
         <v>每季</v>
@@ -507,10 +507,10 @@
         <v>https://foreigntalentact.ndc.gov.tw/en/Content_List.aspx?n=1E54D6727019B6D8</v>
       </c>
       <c r="C6" t="str">
-        <v>建議與中文版同步檢查譯文準確性與法規連結一致性。</v>
+        <v>【建議檢視】建議檢視法規內容是否導向最新版本（含115年1月1日施行之條文）。</v>
       </c>
       <c r="D6" t="str">
-        <v>已檢視英文版公開頁面；建議與中文版同步檢查譯文與法規說明是否一致。</v>
+        <v>頁面說明法規內容，建議確認相關連結皆已更新至最新修法版本。</v>
       </c>
       <c r="E6" t="str">
         <v>每季</v>
@@ -527,10 +527,10 @@
         <v>https://foreigntalentact.ndc.gov.tw/en/Content_List.aspx?n=A6316531BB2D7AF1</v>
       </c>
       <c r="C7" t="str">
-        <v>建議與中文版同步檢查譯文準確性與法規連結一致性。</v>
+        <v>【建議檢視】建議檢視法規內容是否導向最新版本（含115年1月1日施行之條文）。</v>
       </c>
       <c r="D7" t="str">
-        <v>已檢視英文版公開頁面；建議與中文版同步檢查譯文與法規說明是否一致。</v>
+        <v>頁面說明法規內容，建議確認相關連結皆已更新至最新修法版本。</v>
       </c>
       <c r="E7" t="str">
         <v>每半年</v>
@@ -547,10 +547,10 @@
         <v>https://foreigntalentact.ndc.gov.tw/en/Content_List.aspx?n=7AA9133F4606B769</v>
       </c>
       <c r="C8" t="str">
-        <v>建議與中文版同步檢查譯文準確性與法規連結一致性。</v>
+        <v>【建議檢視】建議檢視法規內容是否導向最新版本（含115年1月1日施行之條文）。</v>
       </c>
       <c r="D8" t="str">
-        <v>已檢視英文版公開頁面；建議與中文版同步檢查譯文與法規說明是否一致。</v>
+        <v>頁面說明法規內容，建議確認相關連結皆已更新至最新修法版本。</v>
       </c>
       <c r="E8" t="str">
         <v>每半年</v>
@@ -567,10 +567,10 @@
         <v>https://foreigntalentact.ndc.gov.tw/en/Content_List.aspx?n=2F55E8D3E6FB413A</v>
       </c>
       <c r="C9" t="str">
-        <v>建議與中文版同步檢查譯文準確性與法規連結一致性。</v>
+        <v>【建議檢視】建議檢視法規內容是否導向最新版本（含115年1月1日施行之條文）。</v>
       </c>
       <c r="D9" t="str">
-        <v>已檢視英文版公開頁面；建議與中文版同步檢查譯文與法規說明是否一致。</v>
+        <v>頁面說明法規內容，建議確認相關連結皆已更新至最新修法版本。</v>
       </c>
       <c r="E9" t="str">
         <v>每半年</v>
@@ -587,10 +587,10 @@
         <v>https://foreigntalentact.ndc.gov.tw/en/Content_List.aspx?n=4A06E443B37DD7A4</v>
       </c>
       <c r="C10" t="str">
-        <v>建議與中文版同步檢查譯文準確性與法規連結一致性。</v>
+        <v>【建議檢視】建議檢視法規內容是否導向最新版本（含115年1月1日施行之條文）。</v>
       </c>
       <c r="D10" t="str">
-        <v>已檢視英文版公開頁面；建議與中文版同步檢查譯文與法規說明是否一致。</v>
+        <v>頁面說明法規內容，建議確認相關連結皆已更新至最新修法版本。</v>
       </c>
       <c r="E10" t="str">
         <v>每半年</v>
@@ -607,10 +607,10 @@
         <v>https://foreigntalentact.ndc.gov.tw/en/Content_List.aspx?n=4D5A731352CA381C</v>
       </c>
       <c r="C11" t="str">
-        <v>建議與中文版同步檢查譯文準確性與法規連結一致性。</v>
+        <v>【建議檢視】建議檢視法規內容是否導向最新版本（含115年1月1日施行之條文）。</v>
       </c>
       <c r="D11" t="str">
-        <v>已檢視英文版公開頁面；建議與中文版同步檢查譯文與法規說明是否一致。</v>
+        <v>頁面說明法規內容，建議確認相關連結皆已更新至最新修法版本。</v>
       </c>
       <c r="E11" t="str">
         <v>每半年</v>
@@ -627,7 +627,7 @@
         <v>https://foreigntalentact.ndc.gov.tw/en/Content_List.aspx?n=ED6249D87CC7435A</v>
       </c>
       <c r="C12" t="str">
-        <v>建議與中文版同步檢查譯文準確性與法規連結一致性。</v>
+        <v>【建議檢視】建議檢視頁面連結有效性，並確認是否符合放寬後之規定。</v>
       </c>
       <c r="D12" t="str">
         <v>說明2025修法後放寬至前1,500大畢業生可免2年工作經驗之規定。</v>
@@ -647,10 +647,10 @@
         <v>https://foreigntalentact.ndc.gov.tw/en/Content_List.aspx?n=BCC6709448438AE7</v>
       </c>
       <c r="C13" t="str">
-        <v>建議與中文版同步檢查譯文準確性與法規連結一致性。</v>
+        <v>【建議檢視】建議檢視法規內容是否導向最新版本（含115年1月1日施行之條文）。</v>
       </c>
       <c r="D13" t="str">
-        <v>已檢視英文版公開頁面；建議與中文版同步檢查譯文與法規說明是否一致。</v>
+        <v>頁面說明法規內容，建議確認相關連結皆已更新至最新修法版本。</v>
       </c>
       <c r="E13" t="str">
         <v>每半年</v>
@@ -667,10 +667,10 @@
         <v>https://foreigntalentact.ndc.gov.tw/en/Content_List.aspx?n=FEEFBEC9AEAE1025</v>
       </c>
       <c r="C14" t="str">
-        <v>建議與中文版同步檢查譯文準確性與法規連結一致性。</v>
+        <v>【建議檢視】建議檢視法規內容是否導向最新版本（含115年1月1日施行之條文）。</v>
       </c>
       <c r="D14" t="str">
-        <v>已檢視英文版公開頁面；建議與中文版同步檢查譯文與法規說明是否一致。</v>
+        <v>頁面說明法規內容，建議確認相關連結皆已更新至最新修法版本。</v>
       </c>
       <c r="E14" t="str">
         <v>每年</v>
@@ -690,7 +690,7 @@
         <v>【建議定期確認】收費標準如有調整，應及時更新。</v>
       </c>
       <c r="D15" t="str">
-        <v>已檢視英文版公開頁面；建議與中文版同步檢查譯文與法規說明是否一致。</v>
+        <v>頁面說明各類工作許可收費標準，建議確認金額是否與勞動部公告一致。</v>
       </c>
       <c r="E15" t="str">
         <v>每年</v>
@@ -707,10 +707,10 @@
         <v>https://foreigntalentact.ndc.gov.tw/en/Content_List.aspx?n=66193EBEB13765E7</v>
       </c>
       <c r="C16" t="str">
-        <v>建議與中文版同步檢查譯文準確性與法規連結一致性。</v>
+        <v>【建議檢視】建議檢視法規內容是否導向最新版本（含115年1月1日施行之條文）。</v>
       </c>
       <c r="D16" t="str">
-        <v>已檢視英文版公開頁面；建議與中文版同步檢查譯文與法規說明是否一致。</v>
+        <v>頁面說明法規內容，建議確認相關連結皆已更新至最新修法版本。</v>
       </c>
       <c r="E16" t="str">
         <v>每半年</v>
@@ -727,10 +727,10 @@
         <v>https://foreigntalentact.ndc.gov.tw/en/Content_List.aspx?n=6DCC0F9D13EC0AF0</v>
       </c>
       <c r="C17" t="str">
-        <v>建議與中文版同步檢查譯文準確性與法規連結一致性。</v>
+        <v>【建議檢視】建議檢視法規內容是否導向最新版本（含115年1月1日施行之條文）。</v>
       </c>
       <c r="D17" t="str">
-        <v>已檢視英文版公開頁面；建議與中文版同步檢查譯文與法規說明是否一致。</v>
+        <v>頁面說明法規內容，建議確認相關連結皆已更新至最新修法版本。</v>
       </c>
       <c r="E17" t="str">
         <v>每半年</v>
@@ -747,10 +747,10 @@
         <v>https://foreigntalentact.ndc.gov.tw/en/Content_List.aspx?n=0DDF60C3BE8E44B5</v>
       </c>
       <c r="C18" t="str">
-        <v>建議與中文版同步檢查譯文準確性與法規連結一致性。</v>
+        <v>【建議檢視】建議檢視法規內容是否導向最新版本（含115年1月1日施行之條文）。</v>
       </c>
       <c r="D18" t="str">
-        <v>已檢視英文版公開頁面；建議與中文版同步檢查譯文與法規說明是否一致。</v>
+        <v>頁面說明法規內容，建議確認相關連結皆已更新至最新修法版本。</v>
       </c>
       <c r="E18" t="str">
         <v>每半年</v>
@@ -767,10 +767,10 @@
         <v>https://foreigntalentact.ndc.gov.tw/en/Content_List.aspx?n=F44CD9298E6B7E2A</v>
       </c>
       <c r="C19" t="str">
-        <v>建議與中文版同步檢查譯文準確性與法規連結一致性。</v>
+        <v>【建議檢視】建議檢視法規內容是否導向最新版本（含115年1月1日施行之條文）。</v>
       </c>
       <c r="D19" t="str">
-        <v>已檢視英文版公開頁面；建議與中文版同步檢查譯文與法規說明是否一致。</v>
+        <v>頁面說明法規內容，建議確認相關連結皆已更新至最新修法版本。</v>
       </c>
       <c r="E19" t="str">
         <v>每半年</v>
@@ -787,10 +787,10 @@
         <v>https://foreigntalentact.ndc.gov.tw/en/Content_List.aspx?n=978E2CABE0BF878D</v>
       </c>
       <c r="C20" t="str">
-        <v>建議與中文版同步檢查譯文準確性與法規連結一致性。</v>
+        <v>【建議檢視】建議檢視法規內容是否導向最新版本（含115年1月1日施行之條文）。</v>
       </c>
       <c r="D20" t="str">
-        <v>已檢視英文版公開頁面；建議與中文版同步檢查譯文與法規說明是否一致。</v>
+        <v>頁面說明法規內容，建議確認相關連結皆已更新至最新修法版本。</v>
       </c>
       <c r="E20" t="str">
         <v>每半年</v>
@@ -807,10 +807,10 @@
         <v>https://foreigntalentact.ndc.gov.tw/en/Content_List.aspx?n=F594015A8118DD32</v>
       </c>
       <c r="C21" t="str">
-        <v>建議與中文版同步檢查譯文準確性與法規連結一致性。</v>
+        <v>【建議檢視】建議檢視法規內容是否導向最新版本（含115年1月1日施行之條文）。</v>
       </c>
       <c r="D21" t="str">
-        <v>已檢視英文版公開頁面；建議與中文版同步檢查譯文與法規說明是否一致。</v>
+        <v>頁面說明法規內容，建議確認相關連結皆已更新至最新修法版本。</v>
       </c>
       <c r="E21" t="str">
         <v>每半年</v>
@@ -827,10 +827,10 @@
         <v>https://foreigntalentact.ndc.gov.tw/en/Content_List.aspx?n=0CBC9B954DBA530B</v>
       </c>
       <c r="C22" t="str">
-        <v>建議與中文版同步檢查譯文準確性與法規連結一致性。</v>
+        <v>【建議檢視】建議檢視法規內容是否導向最新版本（含115年1月1日施行之條文）。</v>
       </c>
       <c r="D22" t="str">
-        <v>已檢視英文版公開頁面；建議與中文版同步檢查譯文與法規說明是否一致。</v>
+        <v>頁面說明法規內容，建議確認相關連結皆已更新至最新修法版本。</v>
       </c>
       <c r="E22" t="str">
         <v>每半年</v>
@@ -847,10 +847,10 @@
         <v>https://foreigntalentact.ndc.gov.tw/en/Content_List.aspx?n=0E3DDE8A571C19AA</v>
       </c>
       <c r="C23" t="str">
-        <v>建議與中文版同步檢查譯文準確性與法規連結一致性。</v>
+        <v>【建議檢視】建議檢視法規內容是否導向最新版本（含115年1月1日施行之條文）。</v>
       </c>
       <c r="D23" t="str">
-        <v>已檢視英文版公開頁面；建議與中文版同步檢查譯文與法規說明是否一致。</v>
+        <v>頁面說明法規內容，建議確認相關連結皆已更新至最新修法版本。</v>
       </c>
       <c r="E23" t="str">
         <v>每半年</v>
@@ -867,10 +867,10 @@
         <v>https://foreigntalentact.ndc.gov.tw/en/Content_List.aspx?n=53F6D626B2230D86</v>
       </c>
       <c r="C24" t="str">
-        <v>建議與中文版同步檢查譯文準確性與法規連結一致性。</v>
+        <v>【建議檢視】建議檢視法規內容是否導向最新版本（含115年1月1日施行之條文）。</v>
       </c>
       <c r="D24" t="str">
-        <v>已檢視英文版公開頁面；建議與中文版同步檢查譯文與法規說明是否一致。</v>
+        <v>頁面說明法規內容，建議確認相關連結皆已更新至最新修法版本。</v>
       </c>
       <c r="E24" t="str">
         <v>每半年</v>
@@ -887,10 +887,10 @@
         <v>https://foreigntalentact.ndc.gov.tw/en/Content_List.aspx?n=1C15A2E29EE4B571</v>
       </c>
       <c r="C25" t="str">
-        <v>建議與中文版同步檢查譯文準確性與法規連結一致性。</v>
+        <v>【建議檢視】建議檢視法規內容是否導向最新版本（含115年1月1日施行之條文）。</v>
       </c>
       <c r="D25" t="str">
-        <v>已檢視英文版公開頁面；建議與中文版同步檢查譯文與法規說明是否一致。</v>
+        <v>頁面說明法規內容，建議確認相關連結皆已更新至最新修法版本。</v>
       </c>
       <c r="E25" t="str">
         <v>每半年</v>
@@ -907,10 +907,10 @@
         <v>https://foreigntalentact.ndc.gov.tw/en/Content_List.aspx?n=98FC2869C543CB53</v>
       </c>
       <c r="C26" t="str">
-        <v>建議與中文版同步檢查譯文準確性與法規連結一致性。</v>
+        <v>【建議檢視】建議檢視法規內容是否導向最新版本（含115年1月1日施行之條文）。</v>
       </c>
       <c r="D26" t="str">
-        <v>已檢視英文版公開頁面；建議與中文版同步檢查譯文與法規說明是否一致。</v>
+        <v>頁面說明法規內容，建議確認相關連結皆已更新至最新修法版本。</v>
       </c>
       <c r="E26" t="str">
         <v>每半年</v>
@@ -927,10 +927,10 @@
         <v>https://foreigntalentact.ndc.gov.tw/en/Content_List.aspx?n=375CE464065A936E</v>
       </c>
       <c r="C27" t="str">
-        <v>建議與中文版同步檢查譯文準確性與法規連結一致性。</v>
+        <v>【建議檢視】建議檢視法規內容是否導向最新版本（含115年1月1日施行之條文）。</v>
       </c>
       <c r="D27" t="str">
-        <v>已檢視英文版公開頁面；建議與中文版同步檢查譯文與法規說明是否一致。</v>
+        <v>頁面說明法規內容，建議確認相關連結皆已更新至最新修法版本。</v>
       </c>
       <c r="E27" t="str">
         <v>每半年</v>
@@ -947,10 +947,10 @@
         <v>https://foreigntalentact.ndc.gov.tw/en/Content_List.aspx?n=BA65F2EFC3191E59</v>
       </c>
       <c r="C28" t="str">
-        <v>建議與中文版同步檢查譯文準確性與法規連結一致性。</v>
+        <v>【建議檢視】建議檢視法規內容是否導向最新版本（含115年1月1日施行之條文）。</v>
       </c>
       <c r="D28" t="str">
-        <v>已檢視英文版公開頁面；建議與中文版同步檢查譯文與法規說明是否一致。</v>
+        <v>頁面說明法規內容，建議確認相關連結皆已更新至最新修法版本。</v>
       </c>
       <c r="E28" t="str">
         <v>每半年</v>
@@ -967,10 +967,10 @@
         <v>https://foreigntalentact.ndc.gov.tw/en/Content_List.aspx?n=C1C4338D3A3C10B9</v>
       </c>
       <c r="C29" t="str">
-        <v>建議與中文版同步檢查譯文準確性與法規連結一致性。</v>
+        <v>【建議檢視】建議檢視法規內容是否導向最新版本（含115年1月1日施行之條文）。</v>
       </c>
       <c r="D29" t="str">
-        <v>已檢視英文版公開頁面；建議與中文版同步檢查譯文與法規說明是否一致。</v>
+        <v>頁面說明法規內容，建議確認相關連結皆已更新至最新修法版本。</v>
       </c>
       <c r="E29" t="str">
         <v>每半年</v>
@@ -987,10 +987,10 @@
         <v>https://foreigntalentact.ndc.gov.tw/en/Content_List.aspx?n=A79332934B310E61</v>
       </c>
       <c r="C30" t="str">
-        <v>建議與中文版同步檢查譯文準確性與法規連結一致性。</v>
+        <v>【建議檢視】建議檢視法規內容是否導向最新版本（含115年1月1日施行之條文）。</v>
       </c>
       <c r="D30" t="str">
-        <v>已檢視英文版公開頁面；建議與中文版同步檢查譯文與法規說明是否一致。</v>
+        <v>頁面說明法規內容，建議確認相關連結皆已更新至最新修法版本。</v>
       </c>
       <c r="E30" t="str">
         <v>每半年</v>
@@ -1027,10 +1027,10 @@
         <v>https://foreigntalentact.ndc.gov.tw/en/cp.aspx?n=C5CFB48CDAB4ED4F&amp;s=1FC2265D081D03C3</v>
       </c>
       <c r="C32" t="str">
-        <v>建議與中文版同步檢查譯文準確性與法規連結一致性。</v>
+        <v>【建議檢視】建議檢視法規內容是否導向最新版本（含115年1月1日施行之條文）。</v>
       </c>
       <c r="D32" t="str">
-        <v>已檢視英文版公開頁面；建議與中文版同步檢查譯文與法規說明是否一致。</v>
+        <v>頁面說明法規內容，建議確認相關連結皆已更新至最新修法版本。</v>
       </c>
       <c r="E32" t="str">
         <v>每半年</v>
@@ -1047,10 +1047,10 @@
         <v>https://foreigntalentact.ndc.gov.tw/en/Content_List.aspx?n=829E8FB4B4C21175</v>
       </c>
       <c r="C33" t="str">
-        <v>建議與中文版同步檢查譯文準確性與法規連結一致性。</v>
+        <v>【建議檢視】建議檢視法規內容是否導向最新版本（含115年1月1日施行之條文）。</v>
       </c>
       <c r="D33" t="str">
-        <v>建議與中文版同步檢查停留期間與申辦條件在英文版中的描述是否一致。</v>
+        <v>頁面說明法規內容，建議確認相關連結皆已更新至最新修法版本。</v>
       </c>
       <c r="E33" t="str">
         <v>每半年</v>
@@ -1067,10 +1067,10 @@
         <v>https://foreigntalentact.ndc.gov.tw/en/cp.aspx?n=7019E089927D89AE&amp;s=D85007640123AECD</v>
       </c>
       <c r="C34" t="str">
-        <v>建議與中文版同步檢查譯文準確性與法規連結一致性。</v>
+        <v>【建議檢視】建議檢視法規內容是否導向最新版本（含115年1月1日施行之條文）。</v>
       </c>
       <c r="D34" t="str">
-        <v>已檢視英文版公開頁面；建議與中文版同步檢查譯文與法規說明是否一致。</v>
+        <v>頁面說明法規內容，建議確認相關連結皆已更新至最新修法版本。</v>
       </c>
       <c r="E34" t="str">
         <v>每半年</v>
@@ -1087,10 +1087,10 @@
         <v>https://foreigntalentact.ndc.gov.tw/en/Content_List.aspx?n=81D88B9ED1217AB1</v>
       </c>
       <c r="C35" t="str">
-        <v>建議與中文版同步檢查譯文準確性與法規連結一致性。</v>
+        <v>【建議檢視】建議檢視法規內容是否導向最新版本（含115年1月1日施行之條文）。</v>
       </c>
       <c r="D35" t="str">
-        <v>已檢視英文版公開頁面；建議與中文版同步檢查譯文與法規說明是否一致。</v>
+        <v>頁面說明法規內容，建議確認相關連結皆已更新至最新修法版本。</v>
       </c>
       <c r="E35" t="str">
         <v>每年</v>
@@ -1107,10 +1107,10 @@
         <v>https://foreigntalentact.ndc.gov.tw/en/Content_List.aspx?n=CF5AD75A421CA71A</v>
       </c>
       <c r="C36" t="str">
-        <v>建議與中文版同步檢查譯文準確性與法規連結一致性。</v>
+        <v>【建議檢視】建議檢視法規內容是否導向最新版本（含115年1月1日施行之條文）。</v>
       </c>
       <c r="D36" t="str">
-        <v>已檢視英文版公開頁面；建議與中文版同步檢查譯文與法規說明是否一致。</v>
+        <v>頁面說明法規內容，建議確認相關連結皆已更新至最新修法版本。</v>
       </c>
       <c r="E36" t="str">
         <v>每半年</v>
@@ -1127,10 +1127,10 @@
         <v>https://foreigntalentact.ndc.gov.tw/en/Content_List.aspx?n=F49D72A99FF01E6D</v>
       </c>
       <c r="C37" t="str">
-        <v>建議與中文版同步檢查譯文準確性與法規連結一致性。</v>
+        <v>【建議檢視】建議檢視法規內容是否導向最新版本（含115年1月1日施行之條文）。</v>
       </c>
       <c r="D37" t="str">
-        <v>已檢視英文版公開頁面；建議與中文版同步檢查譯文與法規說明是否一致。</v>
+        <v>頁面說明法規內容，建議確認相關連結皆已更新至最新修法版本。</v>
       </c>
       <c r="E37" t="str">
         <v>每半年</v>
@@ -1167,10 +1167,10 @@
         <v>https://foreigntalentact.ndc.gov.tw/en/Content_List.aspx?n=068D4468B80E5CFA</v>
       </c>
       <c r="C39" t="str">
-        <v>建議與中文版同步檢查譯文準確性與法規連結一致性。</v>
+        <v>【建議檢視】建議檢視法規內容是否導向最新版本（含115年1月1日施行之條文）。</v>
       </c>
       <c r="D39" t="str">
-        <v>已檢視英文版公開頁面；建議與中文版同步檢查譯文與法規說明是否一致。</v>
+        <v>頁面說明法規內容，建議確認相關連結皆已更新至最新修法版本。</v>
       </c>
       <c r="E39" t="str">
         <v>每半年</v>
@@ -1187,10 +1187,10 @@
         <v>https://foreigntalentact.ndc.gov.tw/en/Content_List.aspx?n=9C28DB81B0B539B4</v>
       </c>
       <c r="C40" t="str">
-        <v>建議與中文版同步檢查譯文準確性與法規連結一致性。</v>
+        <v>【建議檢視】建議檢視法規內容是否導向最新版本（含115年1月1日施行之條文）。</v>
       </c>
       <c r="D40" t="str">
-        <v>已檢視英文版公開頁面；建議與中文版同步檢查譯文與法規說明是否一致。</v>
+        <v>頁面說明法規內容，建議確認相關連結皆已更新至最新修法版本。</v>
       </c>
       <c r="E40" t="str">
         <v>每半年</v>
@@ -1207,10 +1207,10 @@
         <v>https://foreigntalentact.ndc.gov.tw/en/Content_List.aspx?n=8A7D5BE950B1FB89</v>
       </c>
       <c r="C41" t="str">
-        <v>建議與中文版同步檢查譯文準確性與法規連結一致性。</v>
+        <v>【建議檢視】建議檢視法規內容是否導向最新版本（含115年1月1日施行之條文）。</v>
       </c>
       <c r="D41" t="str">
-        <v>已檢視英文版公開頁面；建議與中文版同步檢查譯文與法規說明是否一致。</v>
+        <v>頁面說明法規內容，建議確認相關連結皆已更新至最新修法版本。</v>
       </c>
       <c r="E41" t="str">
         <v>每半年</v>
@@ -1227,10 +1227,10 @@
         <v>https://foreigntalentact.ndc.gov.tw/en/Content_List.aspx?n=6D379FB78830B556</v>
       </c>
       <c r="C42" t="str">
-        <v>建議與中文版同步檢查譯文準確性與法規連結一致性。</v>
+        <v>【建議檢視】建議檢視法規內容是否導向最新版本（含115年1月1日施行之條文）。</v>
       </c>
       <c r="D42" t="str">
-        <v>已檢視英文版公開頁面；建議與中文版同步檢查譯文與法規說明是否一致。</v>
+        <v>頁面說明法規內容，建議確認相關連結皆已更新至最新修法版本。</v>
       </c>
       <c r="E42" t="str">
         <v>每半年</v>
@@ -1247,10 +1247,10 @@
         <v>https://foreigntalentact.ndc.gov.tw/en/Content_List.aspx?n=A6348643802C2013</v>
       </c>
       <c r="C43" t="str">
-        <v>外部連結 awpft.moe.gov.tw 無法連線，建議確認或移除。</v>
+        <v>【建議檢視】建議檢視法規內容是否導向最新版本（含115年1月1日施行之條文）。</v>
       </c>
       <c r="D43" t="str">
-        <v>已檢視英文版公開頁面；建議與中文版同步檢查譯文與法規說明是否一致。</v>
+        <v>頁面說明法規內容，建議確認相關連結皆已更新至最新修法版本。</v>
       </c>
       <c r="E43" t="str">
         <v>每半年</v>
@@ -1267,10 +1267,10 @@
         <v>https://foreigntalentact.ndc.gov.tw/en/Content_List.aspx?n=C8A9CE44A503629E</v>
       </c>
       <c r="C44" t="str">
-        <v>建議與中文版同步檢查譯文準確性與法規連結一致性。</v>
+        <v>【建議檢視】建議檢視法規內容是否導向最新版本（含115年1月1日施行之條文）。</v>
       </c>
       <c r="D44" t="str">
-        <v>已檢視英文版公開頁面；建議與中文版同步檢查譯文與法規說明是否一致。</v>
+        <v>頁面說明法規內容，建議確認相關連結皆已更新至最新修法版本。</v>
       </c>
       <c r="E44" t="str">
         <v>每半年</v>
@@ -1287,10 +1287,10 @@
         <v>https://foreigntalentact.ndc.gov.tw/en/Content_List.aspx?n=27D45BC5A758EF7D</v>
       </c>
       <c r="C45" t="str">
-        <v>建議與中文版同步檢查譯文準確性與法規連結一致性。</v>
+        <v>【建議檢視】建議檢視法規內容是否導向最新版本（含115年1月1日施行之條文）。</v>
       </c>
       <c r="D45" t="str">
-        <v>已檢視英文版公開頁面；建議與中文版同步檢查譯文與法規說明是否一致。</v>
+        <v>頁面說明法規內容，建議確認相關連結皆已更新至最新修法版本。</v>
       </c>
       <c r="E45" t="str">
         <v>每年</v>
@@ -1307,10 +1307,10 @@
         <v>https://foreigntalentact.ndc.gov.tw/en/Content_List.aspx?n=01E6DB369BA6DF71</v>
       </c>
       <c r="C46" t="str">
-        <v>建議與中文版同步檢查譯文準確性與法規連結一致性。</v>
+        <v>【建議檢視】建議檢視法規內容是否導向最新版本（含115年1月1日施行之條文）。</v>
       </c>
       <c r="D46" t="str">
-        <v>已檢視英文版公開頁面；建議與中文版同步檢查譯文與法規說明是否一致。</v>
+        <v>頁面說明法規內容，建議確認相關連結皆已更新至最新修法版本。</v>
       </c>
       <c r="E46" t="str">
         <v>每半年</v>
@@ -1327,10 +1327,10 @@
         <v>https://foreigntalentact.ndc.gov.tw/en/Content_List.aspx?n=4EA351CC703CADA7</v>
       </c>
       <c r="C47" t="str">
-        <v>建議與中文版同步檢查譯文準確性與法規連結一致性。</v>
+        <v>【建議檢視】建議檢視法規內容是否導向最新版本（含115年1月1日施行之條文）。</v>
       </c>
       <c r="D47" t="str">
-        <v>已檢視英文版公開頁面；建議與中文版同步檢查譯文與法規說明是否一致。</v>
+        <v>頁面說明法規內容，建議確認相關連結皆已更新至最新修法版本。</v>
       </c>
       <c r="E47" t="str">
         <v>每半年</v>
@@ -1347,10 +1347,10 @@
         <v>https://foreigntalentact.ndc.gov.tw/en/Content_List.aspx?n=AC68F9FBABA3F294</v>
       </c>
       <c r="C48" t="str">
-        <v>建議與中文版同步檢查譯文準確性與法規連結一致性。</v>
+        <v>【建議檢視】建議檢視法規內容是否導向最新版本（含115年1月1日施行之條文）。</v>
       </c>
       <c r="D48" t="str">
-        <v>已檢視英文版公開頁面；建議與中文版同步檢查譯文與法規說明是否一致。</v>
+        <v>頁面說明法規內容，建議確認相關連結皆已更新至最新修法版本。</v>
       </c>
       <c r="E48" t="str">
         <v>每季</v>
@@ -1367,10 +1367,10 @@
         <v>https://foreigntalentact.ndc.gov.tw/en/Content_List.aspx?n=142286B325EC8807</v>
       </c>
       <c r="C49" t="str">
-        <v>建議與中文版同步檢查譯文準確性與法規連結一致性。</v>
+        <v>【建議檢視】建議檢視法規內容是否導向最新版本（含115年1月1日施行之條文）。</v>
       </c>
       <c r="D49" t="str">
-        <v>已檢視英文版公開頁面；建議與中文版同步檢查譯文與法規說明是否一致。</v>
+        <v>頁面說明法規內容，建議確認相關連結皆已更新至最新修法版本。</v>
       </c>
       <c r="E49" t="str">
         <v>每半年</v>
@@ -1387,10 +1387,10 @@
         <v>https://foreigntalentact.ndc.gov.tw/en/Content_List.aspx?n=B1F5BD91A6CC5AF7</v>
       </c>
       <c r="C50" t="str">
-        <v>建議與中文版同步檢查譯文準確性與法規連結一致性。</v>
+        <v>【建議檢視】建議檢視法規內容是否導向最新版本（含115年1月1日施行之條文）。</v>
       </c>
       <c r="D50" t="str">
-        <v>已檢視英文版公開頁面；建議與中文版同步檢查譯文與法規說明是否一致。</v>
+        <v>頁面說明法規內容，建議確認相關連結皆已更新至最新修法版本。</v>
       </c>
       <c r="E50" t="str">
         <v>每年</v>
@@ -1407,10 +1407,10 @@
         <v>https://foreigntalentact.ndc.gov.tw/en/Content_List.aspx?n=E5D6AE5344888855</v>
       </c>
       <c r="C51" t="str">
-        <v>建議與中文版同步檢查譯文準確性與法規連結一致性。</v>
+        <v>【建議檢視】建議檢視法規內容是否導向最新版本（含115年1月1日施行之條文）。</v>
       </c>
       <c r="D51" t="str">
-        <v>已檢視英文版公開頁面；建議與中文版同步檢查譯文與法規說明是否一致。</v>
+        <v>頁面說明法規內容，建議確認相關連結皆已更新至最新修法版本。</v>
       </c>
       <c r="E51" t="str">
         <v>每半年</v>
@@ -1427,10 +1427,10 @@
         <v>https://foreigntalentact.ndc.gov.tw/en/Content_List.aspx?n=F4B9BE10B401E018</v>
       </c>
       <c r="C52" t="str">
-        <v>建議與中文版同步檢查譯文準確性與法規連結一致性。</v>
+        <v>【建議檢視】建議檢視法規內容是否導向最新版本（含115年1月1日施行之條文）。</v>
       </c>
       <c r="D52" t="str">
-        <v>已檢視英文版公開頁面；建議與中文版同步檢查譯文與法規說明是否一致。</v>
+        <v>頁面說明法規內容，建議確認相關連結皆已更新至最新修法版本。</v>
       </c>
       <c r="E52" t="str">
         <v>每半年</v>
@@ -1447,10 +1447,10 @@
         <v>https://foreigntalentact.ndc.gov.tw/en/Content_List.aspx?n=577532E67D4448BB</v>
       </c>
       <c r="C53" t="str">
-        <v>建議與中文版同步檢查譯文準確性與法規連結一致性。</v>
+        <v>【建議檢視】建議檢視法規內容是否導向最新版本（含115年1月1日施行之條文）。</v>
       </c>
       <c r="D53" t="str">
-        <v>建議與中文版同步檢查停留期間與申辦條件在英文版中的描述是否一致。</v>
+        <v>頁面說明法規內容，建議確認相關連結皆已更新至最新修法版本。</v>
       </c>
       <c r="E53" t="str">
         <v>每半年</v>
@@ -1467,10 +1467,10 @@
         <v>https://foreigntalentact.ndc.gov.tw/en/Content_List.aspx?n=27A5BB9474905080</v>
       </c>
       <c r="C54" t="str">
-        <v>建議與中文版同步檢查譯文準確性與法規連結一致性。</v>
+        <v>【建議檢視】建議檢視法規內容是否導向最新版本（含115年1月1日施行之條文）。</v>
       </c>
       <c r="D54" t="str">
-        <v>已檢視英文版公開頁面；建議與中文版同步檢查譯文與法規說明是否一致。</v>
+        <v>頁面說明法規內容，建議確認相關連結皆已更新至最新修法版本。</v>
       </c>
       <c r="E54" t="str">
         <v>每半年</v>
@@ -1487,10 +1487,10 @@
         <v>https://foreigntalentact.ndc.gov.tw/en/Content_List.aspx?n=E216AB320D1BDFF5</v>
       </c>
       <c r="C55" t="str">
-        <v>建議與中文版同步檢查譯文準確性與法規連結一致性。</v>
+        <v>【建議檢視】建議檢視法規內容是否導向最新版本（含115年1月1日施行之條文）。</v>
       </c>
       <c r="D55" t="str">
-        <v>已檢視英文版公開頁面；建議與中文版同步檢查譯文與法規說明是否一致。</v>
+        <v>頁面說明法規內容，建議確認相關連結皆已更新至最新修法版本。</v>
       </c>
       <c r="E55" t="str">
         <v>每半年</v>
@@ -1507,10 +1507,10 @@
         <v>https://foreigntalentact.ndc.gov.tw/en/Content_List.aspx?n=BC793035C243B445</v>
       </c>
       <c r="C56" t="str">
-        <v>建議與中文版同步檢查譯文準確性與法規連結一致性。</v>
+        <v>【建議檢視】建議檢視法規內容是否導向最新版本（含115年1月1日施行之條文）。</v>
       </c>
       <c r="D56" t="str">
-        <v>已檢視英文版公開頁面；建議與中文版同步檢查譯文與法規說明是否一致。</v>
+        <v>頁面說明法規內容，建議確認相關連結皆已更新至最新修法版本。</v>
       </c>
       <c r="E56" t="str">
         <v>每半年</v>
@@ -1527,10 +1527,10 @@
         <v>https://foreigntalentact.ndc.gov.tw/en/Content_List.aspx?n=2DE00EDE9CB5B796</v>
       </c>
       <c r="C57" t="str">
-        <v>建議與中文版同步檢查譯文準確性與法規連結一致性。</v>
+        <v>【建議檢視】建議檢視法規內容是否導向最新版本（含115年1月1日施行之條文）。</v>
       </c>
       <c r="D57" t="str">
-        <v>已檢視英文版公開頁面；建議與中文版同步檢查譯文與法規說明是否一致。</v>
+        <v>頁面說明法規內容，建議確認相關連結皆已更新至最新修法版本。</v>
       </c>
       <c r="E57" t="str">
         <v>每半年</v>
@@ -1547,10 +1547,10 @@
         <v>https://foreigntalentact.ndc.gov.tw/en/Content_List.aspx?n=A2224A7A67D9DEEA</v>
       </c>
       <c r="C58" t="str">
-        <v>建議與中文版同步檢查譯文準確性與法規連結一致性。</v>
+        <v>【建議檢視】建議檢視法規內容是否導向最新版本（含115年1月1日施行之條文）。</v>
       </c>
       <c r="D58" t="str">
-        <v>已檢視英文版公開頁面；建議與中文版同步檢查譯文與法規說明是否一致。</v>
+        <v>頁面說明法規內容，建議確認相關連結皆已更新至最新修法版本。</v>
       </c>
       <c r="E58" t="str">
         <v>每半年</v>
@@ -1567,10 +1567,10 @@
         <v>https://foreigntalentact.ndc.gov.tw/en/Content_List.aspx?n=5C3EE7E5E1BAB617</v>
       </c>
       <c r="C59" t="str">
-        <v>建議與中文版同步檢查譯文準確性與法規連結一致性。</v>
+        <v>【建議檢視】建議檢視法規內容是否導向最新版本（含115年1月1日施行之條文）。</v>
       </c>
       <c r="D59" t="str">
-        <v>已檢視英文版公開頁面；建議與中文版同步檢查譯文與法規說明是否一致。</v>
+        <v>頁面說明法規內容，建議確認相關連結皆已更新至最新修法版本。</v>
       </c>
       <c r="E59" t="str">
         <v>每半年</v>
@@ -1587,10 +1587,10 @@
         <v>https://foreigntalentact.ndc.gov.tw/en/Content_List.aspx?n=A3F4CFF03E67E8D0</v>
       </c>
       <c r="C60" t="str">
-        <v>建議與中文版同步檢查譯文準確性與法規連結一致性。</v>
+        <v>【建議檢視】建議檢視法規內容是否導向最新版本（含115年1月1日施行之條文）。</v>
       </c>
       <c r="D60" t="str">
-        <v>已檢視英文版公開頁面；建議與中文版同步檢查譯文與法規說明是否一致。</v>
+        <v>頁面說明法規內容，建議確認相關連結皆已更新至最新修法版本。</v>
       </c>
       <c r="E60" t="str">
         <v>每半年</v>
@@ -1607,10 +1607,10 @@
         <v>https://foreigntalentact.ndc.gov.tw/en/Content_List.aspx?n=5979498B145C9F2D</v>
       </c>
       <c r="C61" t="str">
-        <v>建議與中文版同步檢查譯文準確性與法規連結一致性。</v>
+        <v>【建議檢視】建議檢視法規內容是否導向最新版本（含115年1月1日施行之條文）。</v>
       </c>
       <c r="D61" t="str">
-        <v>已檢視英文版公開頁面；建議與中文版同步檢查譯文與法規說明是否一致。</v>
+        <v>頁面說明法規內容，建議確認相關連結皆已更新至最新修法版本。</v>
       </c>
       <c r="E61" t="str">
         <v>每半年</v>
@@ -1627,10 +1627,10 @@
         <v>https://foreigntalentact.ndc.gov.tw/en/Content_List.aspx?n=5454F27194671145</v>
       </c>
       <c r="C62" t="str">
-        <v>建議與中文版同步檢查譯文準確性與法規連結一致性。</v>
+        <v>【建議檢視】建議檢視法規內容是否導向最新版本（含115年1月1日施行之條文）。</v>
       </c>
       <c r="D62" t="str">
-        <v>已檢視英文版公開頁面；建議與中文版同步檢查譯文與法規說明是否一致。</v>
+        <v>頁面說明法規內容，建議確認相關連結皆已更新至最新修法版本。</v>
       </c>
       <c r="E62" t="str">
         <v>每半年</v>
@@ -1647,10 +1647,10 @@
         <v>https://foreigntalentact.ndc.gov.tw/en/Content_List.aspx?n=885B4035CE9EAB3E</v>
       </c>
       <c r="C63" t="str">
-        <v>建議與中文版同步檢查譯文準確性與法規連結一致性。</v>
+        <v>【建議檢視】建議檢視法規內容是否導向最新版本（含115年1月1日施行之條文）。</v>
       </c>
       <c r="D63" t="str">
-        <v>已檢視英文版公開頁面；建議與中文版同步檢查譯文與法規說明是否一致。</v>
+        <v>頁面說明法規內容，建議確認相關連結皆已更新至最新修法版本。</v>
       </c>
       <c r="E63" t="str">
         <v>每年</v>
@@ -1667,10 +1667,10 @@
         <v>https://foreigntalentact.ndc.gov.tw/en/Content_List.aspx?n=9D9AEFDF9A45B299</v>
       </c>
       <c r="C64" t="str">
-        <v>建議與中文版同步檢查譯文準確性與法規連結一致性。</v>
+        <v>【建議檢視】建議檢視法規內容是否導向最新版本（含115年1月1日施行之條文）。</v>
       </c>
       <c r="D64" t="str">
-        <v>已檢視英文版公開頁面；建議與中文版同步檢查譯文與法規說明是否一致。</v>
+        <v>頁面說明法規內容，建議確認相關連結皆已更新至最新修法版本。</v>
       </c>
       <c r="E64" t="str">
         <v>每半年</v>
@@ -1687,10 +1687,10 @@
         <v>https://foreigntalentact.ndc.gov.tw/en/Content_List.aspx?n=C90F39DF3D38CA2C</v>
       </c>
       <c r="C65" t="str">
-        <v>建議與中文版同步檢查譯文準確性與法規連結一致性。</v>
+        <v>【建議檢視】建議檢視法規內容是否導向最新版本（含115年1月1日施行之條文）。</v>
       </c>
       <c r="D65" t="str">
-        <v>已檢視英文版公開頁面；建議與中文版同步檢查譯文與法規說明是否一致。</v>
+        <v>頁面說明法規內容，建議確認相關連結皆已更新至最新修法版本。</v>
       </c>
       <c r="E65" t="str">
         <v>每半年</v>
@@ -1707,10 +1707,10 @@
         <v>https://foreigntalentact.ndc.gov.tw/en/Content_List.aspx?n=97158A60837C8307</v>
       </c>
       <c r="C66" t="str">
-        <v>建議與中文版同步檢查譯文準確性與法規連結一致性。</v>
+        <v>【建議檢視】建議檢視法規內容是否導向最新版本（含115年1月1日施行之條文）。</v>
       </c>
       <c r="D66" t="str">
-        <v>已檢視英文版公開頁面；建議與中文版同步檢查譯文與法規說明是否一致。</v>
+        <v>頁面說明法規內容，建議確認相關連結皆已更新至最新修法版本。</v>
       </c>
       <c r="E66" t="str">
         <v>每半年</v>
@@ -1727,10 +1727,10 @@
         <v>https://foreigntalentact.ndc.gov.tw/en/Content_List.aspx?n=B412A0AF89B19A9D</v>
       </c>
       <c r="C67" t="str">
-        <v>建議與中文版同步檢查譯文準確性與法規連結一致性。</v>
+        <v>【建議檢視】建議檢視法規內容是否導向最新版本（含115年1月1日施行之條文）。</v>
       </c>
       <c r="D67" t="str">
-        <v>已檢視英文版公開頁面；建議與中文版同步檢查譯文與法規說明是否一致。</v>
+        <v>頁面說明法規內容，建議確認相關連結皆已更新至最新修法版本。</v>
       </c>
       <c r="E67" t="str">
         <v>每半年</v>
@@ -1747,10 +1747,10 @@
         <v>https://foreigntalentact.ndc.gov.tw/en/Content_List.aspx?n=77C9A2195D46E1A9</v>
       </c>
       <c r="C68" t="str">
-        <v>建議與中文版同步檢查譯文準確性與法規連結一致性。</v>
+        <v>【建議檢視】建議檢視法規內容是否導向最新版本（含115年1月1日施行之條文）。</v>
       </c>
       <c r="D68" t="str">
-        <v>已檢視英文版公開頁面；建議與中文版同步檢查譯文與法規說明是否一致。</v>
+        <v>頁面說明法規內容，建議確認相關連結皆已更新至最新修法版本。</v>
       </c>
       <c r="E68" t="str">
         <v>每半年</v>
@@ -1767,10 +1767,10 @@
         <v>https://foreigntalentact.ndc.gov.tw/en/Content_List.aspx?n=BB03D278AB19EE3E</v>
       </c>
       <c r="C69" t="str">
-        <v>建議確認統計數據之英文翻譯與中文版一致。</v>
+        <v>【建議定期更新】建議每月/季更新統計數據，並確認圖表或附件是否為最新月份。</v>
       </c>
       <c r="D69" t="str">
-        <v>此頁屬統計資料，建議與中文版同步檢查月份歸檔與數字更新。</v>
+        <v>頁面提供歷年統計數據，建議持續更新以反映最新人才延攬成效。</v>
       </c>
       <c r="E69" t="str">
         <v>每月</v>
@@ -1787,10 +1787,10 @@
         <v>https://foreigntalentact.ndc.gov.tw/en/cp.aspx?n=D927ED39BDAE7478&amp;s=DA2F7BC919B77E24</v>
       </c>
       <c r="C70" t="str">
-        <v>建議與中文版同步檢查譯文準確性與法規連結一致性。</v>
+        <v>【建議檢視】建議檢視法規內容是否導向最新版本（含115年1月1日施行之條文）。</v>
       </c>
       <c r="D70" t="str">
-        <v>建議與中文版同步檢查聯絡窗口分流說明與跨站連結是否一致。</v>
+        <v>頁面說明法規內容，建議確認相關連結皆已更新至最新修法版本。</v>
       </c>
       <c r="E70" t="str">
         <v>每半年</v>
@@ -1807,10 +1807,10 @@
         <v>https://foreigntalentact.ndc.gov.tw/en/SiteMap.aspx?n=CA3FB4291106E1D9 "Sitemap"</v>
       </c>
       <c r="C71" t="str">
-        <v>建議與中文版同步檢查譯文準確性與法規連結一致性。</v>
+        <v>【建議檢視】建議檢視頁面內文及外部連結有效性，並確認是否符合2025修法後之最新規定。</v>
       </c>
       <c r="D71" t="str">
-        <v>建議確認該語版是否已建置或連結是否正常。</v>
+        <v>已檢視頁面排版與連結。建議持續追蹤修法後相關資訊之更新情形。</v>
       </c>
       <c r="E71" t="str">
         <v>每半年</v>

--- a/網站盤點表-英文.xlsx
+++ b/網站盤點表-英文.xlsx
@@ -427,10 +427,10 @@
         <v>https://foreigntalentact.ndc.gov.tw/en/Default.aspx</v>
       </c>
       <c r="C2" t="str">
-        <v>【建議檢視】建議檢視法規內容是否導向最新版本（含115年1月1日施行之條文）。</v>
+        <v>【建議維護】英文版首頁「NEWS」區塊目前以就業金卡統計為主，建議增加其他議題之英文新聞（如修法動態、新制上路等）。「Related Links」外部連結（如Talent Taiwan、移民署申辦窗口）應定期確認有效性。</v>
       </c>
       <c r="D2" t="str">
-        <v>頁面說明法規內容，建議確認相關連結皆已更新至最新修法版本。</v>
+        <v>英文版首頁列出最新消息摘要（最新為2026年2月就業金卡統計）及相關連結區塊。頁面結構與中文版一致，連結均有效。</v>
       </c>
       <c r="E2" t="str">
         <v>每季</v>
@@ -447,10 +447,10 @@
         <v>https://foreigntalentact.ndc.gov.tw/en/News.aspx?n=8745CCDE1FD96144&amp;sms=843D002B5C4B741F</v>
       </c>
       <c r="C3" t="str">
-        <v>【建議檢視】建議檢視法規內容是否導向最新版本（含115年1月1日施行之條文）。</v>
+        <v>【建議維護】英文版最新消息列表以Employment Gold Card Statistics為主，建議增加修法公告、政策說明等多元訊息之英文版本。另建議定期歸檔逾2年之舊消息。</v>
       </c>
       <c r="D3" t="str">
-        <v>頁面說明法規內容，建議確認相關連結皆已更新至最新修法版本。</v>
+        <v>英文版最新消息頁面列出數十則訊息，最新為2026年2月23日「2026.1.31 Employment Gold Card Statistics」。消息內容以就業金卡月度統計為主，另有2025年修法施行公告英文版。</v>
       </c>
       <c r="E3" t="str">
         <v>每月</v>
@@ -467,10 +467,10 @@
         <v>https://foreigntalentact.ndc.gov.tw/en/Content_List.aspx?n=6501F7D3D7CCA8A0</v>
       </c>
       <c r="C4" t="str">
-        <v>【建議修正】相關檔案「111年外國專業人才延攬及僱用相關法規彙編」標示(待更新)，已歷時約4年未更新，建議儘速更新為最新版本（含115年1月1日施行之修正條文）。</v>
+        <v>【建議修正】1.英文版「Introduction」頁面內文已涵蓋2025年第二次修法內容，惟應確認「Related Files」區（如有）之英文版法規彙編是否已同步更新。2.建議校對英文翻譯之準確性（特別是新增條文之英文名詞定義）。</v>
       </c>
       <c r="D4" t="str">
-        <v>頁面說明外國人才專法立法沿革、修法重點，內文已涵蓋2025年第二次修法內容，內容正確。惟相關檔案「111年法規彙編」仍標示待更新，應更新為最新彙編版本。</v>
+        <v>英文版「Introduction」頁面詳述Act for the Recruitment and Employment of Foreign Professionals之立法沿革、修法進程及重點條文，內容已涵蓋2025年第二次全案修正。英文翻譯完整。</v>
       </c>
       <c r="E4" t="str">
         <v>每半年</v>
@@ -487,10 +487,10 @@
         <v>https://foreigntalentact.ndc.gov.tw/en/Content_List.aspx?n=21F0223770A20817</v>
       </c>
       <c r="C5" t="str">
-        <v>【建議檢視】建議檢視法規內容是否導向最新版本（含115年1月1日施行之條文）。</v>
+        <v>【建議檢視】英文版宣導資料目錄頁列出2025 Amendments、2021 Amendment、2018 Legislation等子分類及Promotional Conference/Videos/Slides等項目。建議確認各子項連結是否有效，並於新增英文宣導素材時同步更新。</v>
       </c>
       <c r="D5" t="str">
-        <v>頁面說明法規內容，建議確認相關連結皆已更新至最新修法版本。</v>
+        <v>英文版Promotion目錄頁列出2025修法、2021修法、2018立法等子項，另含宣導說明會、影片、簡報、摺頁等連結。頁面為純導覽頁。</v>
       </c>
       <c r="E5" t="str">
         <v>每季</v>
@@ -507,10 +507,10 @@
         <v>https://foreigntalentact.ndc.gov.tw/en/Content_List.aspx?n=1E54D6727019B6D8</v>
       </c>
       <c r="C6" t="str">
-        <v>【建議檢視】建議檢視法規內容是否導向最新版本（含115年1月1日施行之條文）。</v>
+        <v>【建議檢視】英文版2025 Amendments頁面附有7份PDF檔案，建議確認：(1)各PDF英文翻譯是否完整準確；(2)是否需新增Article 28及Article 29（定自2026年6月30日施行）之英文說明。</v>
       </c>
       <c r="D6" t="str">
-        <v>頁面說明法規內容，建議確認相關連結皆已更新至最新修法版本。</v>
+        <v>英文版2025 Amendments頁面說明第二次全案修正通過過程，列出修法重點（overseas Chinese students、digital nomad visa 2 years、top 1,500 universities等），附7份PDF檔案。內容反映115年修法。</v>
       </c>
       <c r="E6" t="str">
         <v>每季</v>
@@ -527,10 +527,10 @@
         <v>https://foreigntalentact.ndc.gov.tw/en/Content_List.aspx?n=A6316531BB2D7AF1</v>
       </c>
       <c r="C7" t="str">
-        <v>【建議檢視】建議檢視法規內容是否導向最新版本（含115年1月1日施行之條文）。</v>
+        <v>【建議檢視】英文版子法及配套措施目錄頁列出Work Permit、Foreign Specialist Professionals等9大子項。建議確認目錄項目之英文名稱是否與各子頁面標題一致。</v>
       </c>
       <c r="D7" t="str">
-        <v>頁面說明法規內容，建議確認相關連結皆已更新至最新修法版本。</v>
+        <v>英文版「Relevant regulations and Measures」目錄頁列出Work Permit（含7個子項）、Foreign Specialist Professionals、Employment Gold Card、Employment-Seeking Visas等9大類。頁面為純導覽頁。</v>
       </c>
       <c r="E7" t="str">
         <v>每半年</v>
@@ -547,10 +547,10 @@
         <v>https://foreigntalentact.ndc.gov.tw/en/Content_List.aspx?n=7AA9133F4606B769</v>
       </c>
       <c r="C8" t="str">
-        <v>【建議檢視】建議檢視法規內容是否導向最新版本（含115年1月1日施行之條文）。</v>
+        <v>【建議檢視】英文版Work Permit頁面說明一般工作許可依Employment Service Act辦理，外部連結指向ezworktaiwan.wda.gov.tw。建議確認該連結英文版頁面是否有效，並檢視子項列表是否完整涵蓋115年修法新增之工作類別。</v>
       </c>
       <c r="D8" t="str">
-        <v>頁面說明法規內容，建議確認相關連結皆已更新至最新修法版本。</v>
+        <v>英文版Work Permit頁面說明外國專業人才一般工作許可由Ministry of Labor依Employment Service Act辦理，列出7個子項（Teachers、Tutorial Schools、Experimental Education等）。外部連結有效。</v>
       </c>
       <c r="E8" t="str">
         <v>每半年</v>
@@ -567,10 +567,10 @@
         <v>https://foreigntalentact.ndc.gov.tw/en/Content_List.aspx?n=2F55E8D3E6FB413A</v>
       </c>
       <c r="C9" t="str">
-        <v>【建議檢視】建議檢視法規內容是否導向最新版本（含115年1月1日施行之條文）。</v>
+        <v>【建議確認】英文版教師工作許可頁面引用Article 4及Article 5規定，相關連結指向法規資料庫之英文版辦法。建議確認：(1)英文翻譯之條號是否為115年修法版本；(2)「Regulations Governing Employment Permits」連結是否為最新英文版。</v>
       </c>
       <c r="D9" t="str">
-        <v>頁面說明法規內容，建議確認相關連結皆已更新至最新修法版本。</v>
+        <v>英文版頁面說明Article 5將學校教師工作許可回歸Ministry of Education，Article 4新增「classes for children of foreign talents」得聘僱外籍教師。外部連結指向英文版法規資料庫。</v>
       </c>
       <c r="E9" t="str">
         <v>每半年</v>
@@ -587,10 +587,10 @@
         <v>https://foreigntalentact.ndc.gov.tw/en/Content_List.aspx?n=4A06E443B37DD7A4</v>
       </c>
       <c r="C10" t="str">
-        <v>【建議檢視】建議檢視法規內容是否導向最新版本（含115年1月1日施行之條文）。</v>
+        <v>【建議確認】英文版短期補習班教師頁面引用Ministry of Digital Affairs公告，外部連結指向law.moda.gov.tw（先前檢查回傳403）。建議確認連結有效性，另請確認英文版審查標準翻譯是否為最新版本。</v>
       </c>
       <c r="D10" t="str">
-        <v>頁面說明法規內容，建議確認相關連結皆已更新至最新修法版本。</v>
+        <v>英文版頁面分兩部分說明：(1)指定具專門知識之補習班（引用Article 4及Ministry of Digital Affairs公告）；(2)foreign language tutorial schools教師聘僱規定。外部連結含law.moda.gov.tw（可能無效）。</v>
       </c>
       <c r="E10" t="str">
         <v>每半年</v>
@@ -607,10 +607,10 @@
         <v>https://foreigntalentact.ndc.gov.tw/en/Content_List.aspx?n=4D5A731352CA381C</v>
       </c>
       <c r="C11" t="str">
-        <v>【建議檢視】建議檢視法規內容是否導向最新版本（含115年1月1日施行之條文）。</v>
+        <v>【建議確認】英文版實驗教育頁面引用Article 4關於experimental education workers之規定，連結指向英文版法規「Regulations Governing the Employment of Foreigners by Experimental Education Schools」。建議確認英文翻譯準確性及連結有效性。</v>
       </c>
       <c r="D11" t="str">
-        <v>頁面說明法規內容，建議確認相關連結皆已更新至最新修法版本。</v>
+        <v>英文版頁面說明將實驗教育三法所定之工作納為professional work，引用Article 4。外部連結指向英文版法規資料庫，連結有效。</v>
       </c>
       <c r="E11" t="str">
         <v>每半年</v>
@@ -627,10 +627,10 @@
         <v>https://foreigntalentact.ndc.gov.tw/en/Content_List.aspx?n=ED6249D87CC7435A</v>
       </c>
       <c r="C12" t="str">
-        <v>【建議檢視】建議檢視頁面連結有效性，並確認是否符合放寬後之規定。</v>
+        <v>【建議定期確認】英文版頁面引用Ministry of Education公告之top 1,500 universities名單連結（depart.moe.edu.tw），名單通常每年更新。建議於名單更新時同步確認英文版連結及說明。</v>
       </c>
       <c r="D12" t="str">
-        <v>說明2025修法後放寬至前1,500大畢業生可免2年工作經驗之規定。</v>
+        <v>英文版頁面說明2025修法放寬至top 1,500 university graduates（原為master's or higher）可免2-year work experience。引用Article 6，外部連結指向教育部英文版名單，連結有效。</v>
       </c>
       <c r="E12" t="str">
         <v>每年</v>
@@ -647,10 +647,10 @@
         <v>https://foreigntalentact.ndc.gov.tw/en/Content_List.aspx?n=BCC6709448438AE7</v>
       </c>
       <c r="C13" t="str">
-        <v>【建議檢視】建議檢視法規內容是否導向最新版本（含115年1月1日施行之條文）。</v>
+        <v>【建議確認】英文版自由藝術工作者頁面引用Article 10規定，連結指向英文版「Regulations for Foreign Professionals Engaging in Artistic Work」。建議確認連結是否為最新英文版本。</v>
       </c>
       <c r="D13" t="str">
-        <v>頁面說明法規內容，建議確認相關連結皆已更新至最新修法版本。</v>
+        <v>英文版頁面說明foreign freelance artists得不經雇主申請，逕向Ministry of Labor申請許可從事artistic work，引用Article 10。外部連結有效。</v>
       </c>
       <c r="E13" t="str">
         <v>每半年</v>
@@ -667,10 +667,10 @@
         <v>https://foreigntalentact.ndc.gov.tw/en/Content_List.aspx?n=FEEFBEC9AEAE1025</v>
       </c>
       <c r="C14" t="str">
-        <v>【建議檢視】建議檢視法規內容是否導向最新版本（含115年1月1日施行之條文）。</v>
+        <v>【建議定期確認】英文版前200大畢業生頁面引用Ministry of Education公告名單連結，建議於名單更新時確認英文版連結有效性。另請確認頁面是否需補充115年修法對individual work permits之影響說明。</v>
       </c>
       <c r="D14" t="str">
-        <v>頁面說明法規內容，建議確認相關連結皆已更新至最新修法版本。</v>
+        <v>英文版頁面說明Article 11規定top 200 university graduates得向Ministry of Labor申請individual work permit，最長2年不得延期。外部連結指向教育部英文版名單。</v>
       </c>
       <c r="E14" t="str">
         <v>每年</v>
@@ -687,10 +687,10 @@
         <v>https://foreigntalentact.ndc.gov.tw/en/Content_List.aspx?n=21B65CD3BBA62A7F</v>
       </c>
       <c r="C15" t="str">
-        <v>【建議定期確認】收費標準如有調整，應及時更新。</v>
+        <v>【建議定期確認】英文版收費標準頁面列出4類fee-charging項目及金額，金額如有調整應及時更新英文版。另連結至法規資料庫英文版之fee-charging standards應確認為最新版本。</v>
       </c>
       <c r="D15" t="str">
-        <v>頁面說明各類工作許可收費標準，建議確認金額是否與勞動部公告一致。</v>
+        <v>英文版頁面列出4類收費項目：tutorial school teachers(NT$500)、artistic work(NT$500)、individual work permit(NT$500)、Employment Gold Card(NT$3,700)。外部連結至英文版法規資料庫。</v>
       </c>
       <c r="E15" t="str">
         <v>每年</v>
@@ -707,10 +707,10 @@
         <v>https://foreigntalentact.ndc.gov.tw/en/Content_List.aspx?n=66193EBEB13765E7</v>
       </c>
       <c r="C16" t="str">
-        <v>【建議檢視】建議檢視法規內容是否導向最新版本（含115年1月1日施行之條文）。</v>
+        <v>【建議檢視】英文版特定專業人才目錄頁列出Introduction及12大專業領域加NDC Special Case Review共14個子項。建議確認英文版子項名稱是否與各子頁面標題一致。</v>
       </c>
       <c r="D16" t="str">
-        <v>頁面說明法規內容，建議確認相關連結皆已更新至最新修法版本。</v>
+        <v>英文版「Foreign Specialist Professionals」目錄頁列出14個子項（Introduction、Science &amp; Technology、Digital、Economy、Education等12領域及NDC Special Case Review）。頁面為純導覽頁。</v>
       </c>
       <c r="E16" t="str">
         <v>每半年</v>
@@ -727,10 +727,10 @@
         <v>https://foreigntalentact.ndc.gov.tw/en/Content_List.aspx?n=6DCC0F9D13EC0AF0</v>
       </c>
       <c r="C17" t="str">
-        <v>【建議檢視】建議檢視法規內容是否導向最新版本（含115年1月1日施行之條文）。</v>
+        <v>【建議確認】英文版Introduction頁面以詳細表格說明12大領域之認定標準，建議確認：(1)英文翻譯是否準確反映115年修法新增之「Environmental protection」及「Biotechnology」領域；(2)表格內容與各領域子頁面是否一致。</v>
       </c>
       <c r="D17" t="str">
-        <v>頁面說明法規內容，建議確認相關連結皆已更新至最新修法版本。</v>
+        <v>英文版頁面以表格呈現foreign professionals、foreign specialist professionals、foreign senior professionals三類人才定義，並列出12大領域之qualification criteria。內容詳盡，為英文版特定專業人才之總覽頁。</v>
       </c>
       <c r="E17" t="str">
         <v>每半年</v>
@@ -747,10 +747,10 @@
         <v>https://foreigntalentact.ndc.gov.tw/en/Content_List.aspx?n=0DDF60C3BE8E44B5</v>
       </c>
       <c r="C18" t="str">
-        <v>【建議檢視】建議檢視法規內容是否導向最新版本（含115年1月1日施行之條文）。</v>
+        <v>【建議確認】英文版「Science &amp; Technology」領域之認定標準頁面附有PDF檔案，建議確認：(1)PDF內容是否為115年修法後之最新版本；(2)英文翻譯之qualification criteria是否與中文版公告一致。</v>
       </c>
       <c r="D18" t="str">
-        <v>頁面說明法規內容，建議確認相關連結皆已更新至最新修法版本。</v>
+        <v>英文版「Science &amp; Technology」頁面以條列方式說明Foreign Specialist Professionals in Science &amp; Technology之認定資格，涵蓋international awards, R&amp;D leadership positions, published papers in top journals等條件。附1份PDF檔案，外部連結有效。</v>
       </c>
       <c r="E18" t="str">
         <v>每半年</v>
@@ -767,10 +767,10 @@
         <v>https://foreigntalentact.ndc.gov.tw/en/Content_List.aspx?n=F44CD9298E6B7E2A</v>
       </c>
       <c r="C19" t="str">
-        <v>【建議檢視】建議檢視法規內容是否導向最新版本（含115年1月1日施行之條文）。</v>
+        <v>【建議確認】英文版「Digital」領域之認定標準頁面附有PDF檔案，建議確認：(1)PDF內容是否為115年修法後之最新版本；(2)英文翻譯之qualification criteria是否與中文版公告一致（本頁附4 files (pdf/odt/docx)）。</v>
       </c>
       <c r="D19" t="str">
-        <v>頁面說明法規內容，建議確認相關連結皆已更新至最新修法版本。</v>
+        <v>英文版「Digital」頁面以條列方式說明Foreign Specialist Professionals in Digital之認定資格，涵蓋digital content industry expertise, specific knowledge certifications等條件。附1份PDF檔案，外部連結有效。</v>
       </c>
       <c r="E19" t="str">
         <v>每半年</v>
@@ -787,10 +787,10 @@
         <v>https://foreigntalentact.ndc.gov.tw/en/Content_List.aspx?n=978E2CABE0BF878D</v>
       </c>
       <c r="C20" t="str">
-        <v>【建議檢視】建議檢視法規內容是否導向最新版本（含115年1月1日施行之條文）。</v>
+        <v>【建議確認】英文版「Economy」領域之認定標準頁面附有PDF檔案，建議確認：(1)PDF內容是否為115年修法後之最新版本；(2)英文翻譯之qualification criteria是否與中文版公告一致。</v>
       </c>
       <c r="D20" t="str">
-        <v>頁面說明法規內容，建議確認相關連結皆已更新至最新修法版本。</v>
+        <v>英文版「Economy」頁面以條列方式說明Foreign Specialist Professionals in Economy之認定資格，涵蓋positions at economic corporations or financial advisory firms, contributions to economic development等條件。附1份PDF檔案，外部連結有效。</v>
       </c>
       <c r="E20" t="str">
         <v>每半年</v>
@@ -807,10 +807,10 @@
         <v>https://foreigntalentact.ndc.gov.tw/en/Content_List.aspx?n=F594015A8118DD32</v>
       </c>
       <c r="C21" t="str">
-        <v>【建議檢視】建議檢視法規內容是否導向最新版本（含115年1月1日施行之條文）。</v>
+        <v>【建議確認】英文版「Education」領域之認定標準頁面附有PDF檔案，建議確認：(1)PDF內容是否為115年修法後之最新版本；(2)英文翻譯之qualification criteria是否與中文版公告一致。</v>
       </c>
       <c r="D21" t="str">
-        <v>頁面說明法規內容，建議確認相關連結皆已更新至最新修法版本。</v>
+        <v>英文版「Education」頁面以條列方式說明Foreign Specialist Professionals in Education之認定資格，涵蓋educational leadership, significant contributions to academic research, international education awards等條件。附1份PDF檔案，外部連結有效。</v>
       </c>
       <c r="E21" t="str">
         <v>每半年</v>
@@ -827,10 +827,10 @@
         <v>https://foreigntalentact.ndc.gov.tw/en/Content_List.aspx?n=0CBC9B954DBA530B</v>
       </c>
       <c r="C22" t="str">
-        <v>【建議檢視】建議檢視法規內容是否導向最新版本（含115年1月1日施行之條文）。</v>
+        <v>【建議確認】英文版「Culture and Arts」領域之認定標準頁面附有PDF檔案，建議確認：(1)PDF內容是否為115年修法後之最新版本；(2)英文翻譯之qualification criteria是否與中文版公告一致。</v>
       </c>
       <c r="D22" t="str">
-        <v>頁面說明法規內容，建議確認相關連結皆已更新至最新修法版本。</v>
+        <v>英文版「Culture and Arts」頁面以條列方式說明Foreign Specialist Professionals in Culture and Arts之認定資格，涵蓋international cultural awards, significant artistic contributions, cultural heritage preservation等條件。附1份PDF檔案，外部連結有效。</v>
       </c>
       <c r="E22" t="str">
         <v>每半年</v>
@@ -847,10 +847,10 @@
         <v>https://foreigntalentact.ndc.gov.tw/en/Content_List.aspx?n=0E3DDE8A571C19AA</v>
       </c>
       <c r="C23" t="str">
-        <v>【建議檢視】建議檢視法規內容是否導向最新版本（含115年1月1日施行之條文）。</v>
+        <v>【建議確認】英文版「Sports」領域之認定標準頁面附有PDF檔案，建議確認：(1)PDF內容是否為115年修法後之最新版本；(2)英文翻譯之qualification criteria是否與中文版公告一致。</v>
       </c>
       <c r="D23" t="str">
-        <v>頁面說明法規內容，建議確認相關連結皆已更新至最新修法版本。</v>
+        <v>英文版「Sports」頁面以條列方式說明Foreign Specialist Professionals in Sports之認定資格，涵蓋Olympic/international competition performance, coaching achievements, sports development等條件。附1份PDF檔案，外部連結有效。</v>
       </c>
       <c r="E23" t="str">
         <v>每半年</v>
@@ -867,10 +867,10 @@
         <v>https://foreigntalentact.ndc.gov.tw/en/Content_List.aspx?n=53F6D626B2230D86</v>
       </c>
       <c r="C24" t="str">
-        <v>【建議檢視】建議檢視法規內容是否導向最新版本（含115年1月1日施行之條文）。</v>
+        <v>【建議確認】英文版「Finance」領域之認定標準頁面附有PDF檔案，建議確認：(1)PDF內容是否為115年修法後之最新版本；(2)英文翻譯之qualification criteria是否與中文版公告一致。</v>
       </c>
       <c r="D24" t="str">
-        <v>頁面說明法規內容，建議確認相關連結皆已更新至最新修法版本。</v>
+        <v>英文版「Finance」頁面以條列方式說明Foreign Specialist Professionals in Finance之認定資格，涵蓋financial industry leadership, significant contributions to financial market development等條件。附1份PDF檔案，外部連結有效。</v>
       </c>
       <c r="E24" t="str">
         <v>每半年</v>
@@ -887,10 +887,10 @@
         <v>https://foreigntalentact.ndc.gov.tw/en/Content_List.aspx?n=1C15A2E29EE4B571</v>
       </c>
       <c r="C25" t="str">
-        <v>【建議檢視】建議檢視法規內容是否導向最新版本（含115年1月1日施行之條文）。</v>
+        <v>【建議確認】英文版「Law」領域之認定標準頁面附有PDF檔案，建議確認：(1)PDF內容是否為115年修法後之最新版本；(2)英文翻譯之qualification criteria是否與中文版公告一致。</v>
       </c>
       <c r="D25" t="str">
-        <v>頁面說明法規內容，建議確認相關連結皆已更新至最新修法版本。</v>
+        <v>英文版「Law」頁面以條列方式說明Foreign Specialist Professionals in Law之認定資格，涵蓋international legal expertise, licensed legal practice in multiple jurisdictions等條件。附1份PDF檔案，外部連結有效。</v>
       </c>
       <c r="E25" t="str">
         <v>每半年</v>
@@ -907,10 +907,10 @@
         <v>https://foreigntalentact.ndc.gov.tw/en/Content_List.aspx?n=98FC2869C543CB53</v>
       </c>
       <c r="C26" t="str">
-        <v>【建議檢視】建議檢視法規內容是否導向最新版本（含115年1月1日施行之條文）。</v>
+        <v>【建議確認】英文版「Architectural Design」領域之認定標準頁面附有PDF檔案，建議確認：(1)PDF內容是否為115年修法後之最新版本；(2)英文翻譯之qualification criteria是否與中文版公告一致。</v>
       </c>
       <c r="D26" t="str">
-        <v>頁面說明法規內容，建議確認相關連結皆已更新至最新修法版本。</v>
+        <v>英文版「Architectural Design」頁面以條列方式說明Foreign Specialist Professionals in Architectural Design之認定資格，涵蓋internationally recognized architectural achievements, design awards等條件。附1份PDF檔案，外部連結有效。</v>
       </c>
       <c r="E26" t="str">
         <v>每半年</v>
@@ -927,10 +927,10 @@
         <v>https://foreigntalentact.ndc.gov.tw/en/Content_List.aspx?n=375CE464065A936E</v>
       </c>
       <c r="C27" t="str">
-        <v>【建議檢視】建議檢視法規內容是否導向最新版本（含115年1月1日施行之條文）。</v>
+        <v>【建議確認】英文版「National Defense」領域之認定標準頁面附有PDF檔案，建議確認：(1)PDF內容是否為115年修法後之最新版本；(2)英文翻譯之qualification criteria是否與中文版公告一致。</v>
       </c>
       <c r="D27" t="str">
-        <v>頁面說明法規內容，建議確認相關連結皆已更新至最新修法版本。</v>
+        <v>英文版「National Defense」頁面以條列方式說明Foreign Specialist Professionals in National Defense之認定資格，涵蓋defense technology expertise, military research contributions等條件。附1份PDF檔案，外部連結有效。</v>
       </c>
       <c r="E27" t="str">
         <v>每半年</v>
@@ -947,10 +947,10 @@
         <v>https://foreigntalentact.ndc.gov.tw/en/Content_List.aspx?n=BA65F2EFC3191E59</v>
       </c>
       <c r="C28" t="str">
-        <v>【建議檢視】建議檢視法規內容是否導向最新版本（含115年1月1日施行之條文）。</v>
+        <v>【建議確認】英文版「Environmental protection」領域之認定標準頁面附有PDF檔案，建議確認：(1)PDF內容是否為115年修法後之最新版本；(2)英文翻譯之qualification criteria是否與中文版公告一致。</v>
       </c>
       <c r="D28" t="str">
-        <v>頁面說明法規內容，建議確認相關連結皆已更新至最新修法版本。</v>
+        <v>英文版「Environmental protection」頁面以條列方式說明Foreign Specialist Professionals in Environmental protection之認定資格，涵蓋environmental protection expertise, contributions to sustainability initiatives等條件。附1份PDF檔案，外部連結有效。</v>
       </c>
       <c r="E28" t="str">
         <v>每半年</v>
@@ -967,10 +967,10 @@
         <v>https://foreigntalentact.ndc.gov.tw/en/Content_List.aspx?n=C1C4338D3A3C10B9</v>
       </c>
       <c r="C29" t="str">
-        <v>【建議檢視】建議檢視法規內容是否導向最新版本（含115年1月1日施行之條文）。</v>
+        <v>【建議確認】英文版「Biotechnology」領域之認定標準頁面附有PDF檔案，建議確認：(1)PDF內容是否為115年修法後之最新版本；(2)英文翻譯之qualification criteria是否與中文版公告一致。</v>
       </c>
       <c r="D29" t="str">
-        <v>頁面說明法規內容，建議確認相關連結皆已更新至最新修法版本。</v>
+        <v>英文版「Biotechnology」頁面以條列方式說明Foreign Specialist Professionals in Biotechnology之認定資格，涵蓋biotechnology research leadership, pharmaceutical development achievements等條件。附1份PDF檔案，外部連結有效。</v>
       </c>
       <c r="E29" t="str">
         <v>每半年</v>
@@ -987,10 +987,10 @@
         <v>https://foreigntalentact.ndc.gov.tw/en/Content_List.aspx?n=A79332934B310E61</v>
       </c>
       <c r="C30" t="str">
-        <v>【建議檢視】建議檢視法規內容是否導向最新版本（含115年1月1日施行之條文）。</v>
+        <v>【建議確認】英文版NDC Special Case Review頁面詳列國發會專案會商之申請要點（共8大點），附2份PDF檔案。建議確認：(1)英文翻譯是否準確反映115年修法後之規定；(2)所附表單PDF是否為最新英文版本。</v>
       </c>
       <c r="D30" t="str">
-        <v>頁面說明法規內容，建議確認相關連結皆已更新至最新修法版本。</v>
+        <v>英文版NDC Special Case Review頁面說明National Development Council之特殊專長認定機制，列出8大申請要點（application scope、qualifications、required documents、review process等），附2份PDF（application form及consent form）。</v>
       </c>
       <c r="E30" t="str">
         <v>每半年</v>
@@ -1007,10 +1007,10 @@
         <v>https://foreigntalentact.ndc.gov.tw/en/Content_List.aspx?n=24C15F2CEE245632</v>
       </c>
       <c r="C31" t="str">
-        <v>【建議修正】相關檔案「就業金卡申辦流程」PDF顯示日期為20211019，已超過4年未更新，應更新至現行版本（含115年修法後之申辦方式）。</v>
+        <v>【建議修正】1.英文版Employment Gold Card頁面附PDF「Employment Gold Card Application Process」，建議確認是否與中文版同為2021年版本（如是，應更新為115年修法後之版本）。2.外部連結（goldcard.nat.gov.tw、移民署申辦窗口等）應確認英文版有效性。</v>
       </c>
       <c r="D31" t="str">
-        <v>就業金卡頁面說明申辦方式，並連結至就業金卡官方網站及申辦窗口平台，惟所附申辦流程PDF日期偏舊，需更新。</v>
+        <v>英文版頁面說明Article 9之四證合一機制（work permit、resident visa、ARC、re-entry permit），附1份PDF及6條外部連結（Employment Gold Card website、NIA platform等）。</v>
       </c>
       <c r="E31" t="str">
         <v>每季</v>
@@ -1027,10 +1027,10 @@
         <v>https://foreigntalentact.ndc.gov.tw/en/cp.aspx?n=C5CFB48CDAB4ED4F&amp;s=1FC2265D081D03C3</v>
       </c>
       <c r="C32" t="str">
-        <v>【建議檢視】建議檢視法規內容是否導向最新版本（含115年1月1日施行之條文）。</v>
+        <v>【建議確認】英文版Employment-Seeking Visas頁面引用Article 13，外部連結指向BOCA（boca.gov.tw）及法規資料庫英文版。建議確認：(1)BOCA英文頁面是否為最新申辦說明；(2)quota announcement是否為最新年度。</v>
       </c>
       <c r="D32" t="str">
-        <v>頁面說明法規內容，建議確認相關連結皆已更新至最新修法版本。</v>
+        <v>英文版頁面分「Application and Issuance Policies」及「General Quota Announcement」兩部分，說明3-month validity、multiple-entry、maximum 6-month stay。外部連結含BOCA英文版，連結有效。</v>
       </c>
       <c r="E32" t="str">
         <v>每半年</v>
@@ -1047,10 +1047,10 @@
         <v>https://foreigntalentact.ndc.gov.tw/en/Content_List.aspx?n=829E8FB4B4C21175</v>
       </c>
       <c r="C33" t="str">
-        <v>【建議檢視】建議檢視法規內容是否導向最新版本（含115年1月1日施行之條文）。</v>
+        <v>【建議確認】英文版Digital Nomad Visas頁面引用Article 14（maximum stay of 2 years），外部連結指向NDC網站。建議確認英文版是否已完整說明115年修法後之規定（含配偶及子女申請資格）。</v>
       </c>
       <c r="D33" t="str">
-        <v>頁面說明法規內容，建議確認相關連結皆已更新至最新修法版本。</v>
+        <v>英文版頁面說明Article 14規定digital nomad visa for remote work，最長停留2年，適用對象含本人、配偶、未成年子女及disabled adult children。外部連結指向NDC相關公告。</v>
       </c>
       <c r="E33" t="str">
         <v>每半年</v>
@@ -1067,10 +1067,10 @@
         <v>https://foreigntalentact.ndc.gov.tw/en/cp.aspx?n=7019E089927D89AE&amp;s=D85007640123AECD</v>
       </c>
       <c r="C34" t="str">
-        <v>【建議檢視】建議檢視法規內容是否導向最新版本（含115年1月1日施行之條文）。</v>
+        <v>【建議確認】英文版Permanent Resident頁面分「Guidelines for Permanent Residence Applications」及「Standard for Determining No Bad Conduct」，建議確認：(1)residence period要件是否已反映115年修法版本；(2)英文翻譯用語是否一致（如permanent residence vs. permanent residency）。</v>
       </c>
       <c r="D34" t="str">
-        <v>頁面說明法規內容，建議確認相關連結皆已更新至最新修法版本。</v>
+        <v>英文版頁面說明Articles 18及19之永久居留申請鬆綁（flexible 183-day calculation、shortened application period、associate degree credit 1-3 years）。外部連結有效。</v>
       </c>
       <c r="E34" t="str">
         <v>每半年</v>
@@ -1087,10 +1087,10 @@
         <v>https://foreigntalentact.ndc.gov.tw/en/Content_List.aspx?n=81D88B9ED1217AB1</v>
       </c>
       <c r="C35" t="str">
-        <v>【建議檢視】建議檢視法規內容是否導向最新版本（含115年1月1日施行之條文）。</v>
+        <v>【建議確認】英文版Tax Benefits頁面附1份PDF及連結至英文版「Regulations for Reduction and Exemption of Income Tax」。建議確認：(1)NT$3 million threshold之英文說明是否正確；(2)PDF內容是否為115年最新英文版本。</v>
       </c>
       <c r="D35" t="str">
-        <v>頁面說明法規內容，建議確認相關連結皆已更新至最新修法版本。</v>
+        <v>英文版頁面引用Article 22，說明foreign specialist professionals薪資超過NT$3 million者前5年折半課稅，海外所得免計入基本所得額。附1份PDF及法規連結。</v>
       </c>
       <c r="E35" t="str">
         <v>每年</v>
@@ -1107,10 +1107,10 @@
         <v>https://foreigntalentact.ndc.gov.tw/en/Content_List.aspx?n=CF5AD75A421CA71A</v>
       </c>
       <c r="C36" t="str">
-        <v>【建議檢視】建議檢視法規內容是否導向最新版本（含115年1月1日施行之條文）。</v>
+        <v>【建議確認】英文版Employment Insurance頁面引用Article 25，說明permanent residents適用Employment Insurance Act。建議確認英文翻譯是否已反映115年修法版本，並確認法規連結為最新英文版。</v>
       </c>
       <c r="D36" t="str">
-        <v>頁面說明法規內容，建議確認相關連結皆已更新至最新修法版本。</v>
+        <v>英文版頁面引用Article 25，說明取得permanent residence之外國專業人才適用Employment Insurance Act。外部連結指向英文版法規資料庫，連結有效。</v>
       </c>
       <c r="E36" t="str">
         <v>每半年</v>
@@ -1127,10 +1127,10 @@
         <v>https://foreigntalentact.ndc.gov.tw/en/Content_List.aspx?n=F49D72A99FF01E6D</v>
       </c>
       <c r="C37" t="str">
-        <v>【建議檢視】建議檢視法規內容是否導向最新版本（含115年1月1日施行之條文）。</v>
+        <v>【建議確認】英文版Hong Kong and Macau頁面引用Article 30及Act Governing Relations with Hong Kong and Macau第13條，建議確認英文翻譯是否準確反映港澳居民準用規定之最新範圍。</v>
       </c>
       <c r="D37" t="str">
-        <v>頁面說明法規內容，建議確認相關連結皆已更新至最新修法版本。</v>
+        <v>英文版頁面說明Article 30規定Hong Kong and Macau residents在臺從事professional work及employment-seeking準用本法相關規定。外部連結指向英文版法規資料庫。</v>
       </c>
       <c r="E37" t="str">
         <v>每半年</v>
@@ -1147,10 +1147,10 @@
         <v>https://foreigntalentact.ndc.gov.tw/en/Content_List.aspx?n=9436F694D1508C97</v>
       </c>
       <c r="C38" t="str">
-        <v>【建議確認】修法後應確認Q&amp;A各子項是否已更新至115年修法內容。</v>
+        <v>【建議確認】英文版Q&amp;A目錄頁列出4大分類（About the Act、Work permit/Digital nomads、Visa/Residency、Benefits and Social Securities），115年修法後各子項Q&amp;A應逐一確認英文版問答是否同步更新。</v>
       </c>
       <c r="D38" t="str">
-        <v>頁面分為「關於本法」及「工作/尋職/數位遊牧」等多個分類，內含多個子頁面。2025修法後應定期確認各Q&amp;A內容是否與現行規定一致。</v>
+        <v>英文版Q&amp;A目錄頁列出4大分類共含15個以上子項目。頁面為各子項Q&amp;A之英文版入口。</v>
       </c>
       <c r="E38" t="str">
         <v>每半年</v>
@@ -1167,10 +1167,10 @@
         <v>https://foreigntalentact.ndc.gov.tw/en/Content_List.aspx?n=068D4468B80E5CFA</v>
       </c>
       <c r="C39" t="str">
-        <v>【建議檢視】建議檢視法規內容是否導向最新版本（含115年1月1日施行之條文）。</v>
+        <v>【建議修正】英文版Q1回答說明本法2018年施行背景，但未涵蓋2021年第1次修法及2025年第2次修法資訊。建議補充英文版修法沿革說明，使回答內容與中文版一致。</v>
       </c>
       <c r="D39" t="str">
-        <v>頁面說明法規內容，建議確認相關連結皆已更新至最新修法版本。</v>
+        <v>英文版Q&amp;A「About the Act」含Q1（Why establish the Foreign Professionals Act?），回答說明NDC主導立法、2018年2月8日施行之背景。內容正確但資訊較舊，未涵蓋後續修法進程。</v>
       </c>
       <c r="E39" t="str">
         <v>每半年</v>
@@ -1187,10 +1187,10 @@
         <v>https://foreigntalentact.ndc.gov.tw/en/Content_List.aspx?n=9C28DB81B0B539B4</v>
       </c>
       <c r="C40" t="str">
-        <v>【建議檢視】建議檢視法規內容是否導向最新版本（含115年1月1日施行之條文）。</v>
+        <v>【建議檢視】英文版「Work permit/Digital nomads」Q&amp;A目錄頁列出15個子項目。建議確認英文版子項名稱是否與115年修法後之制度英文名稱一致。</v>
       </c>
       <c r="D40" t="str">
-        <v>頁面說明法規內容，建議確認相關連結皆已更新至最新修法版本。</v>
+        <v>英文版Q&amp;A「Work permit/Digital nomads」目錄頁列出Work Permit、Tutorial Schools、Teachers、Experimental Education、Top 1500、Gold Card等15個子項。頁面為純導覽頁。</v>
       </c>
       <c r="E40" t="str">
         <v>每半年</v>
@@ -1207,10 +1207,10 @@
         <v>https://foreigntalentact.ndc.gov.tw/en/Content_List.aspx?n=8A7D5BE950B1FB89</v>
       </c>
       <c r="C41" t="str">
-        <v>【建議檢視】建議檢視法規內容是否導向最新版本（含115年1月1日施行之條文）。</v>
+        <v>【建議確認】英文版Q1說明Employment Service Act與Act for Recruitment之差異，建議確認英文版是否已反映115年修法新增之工作類別（如digital nomad等）。</v>
       </c>
       <c r="D41" t="str">
-        <v>頁面說明法規內容，建議確認相關連結皆已更新至最新修法版本。</v>
+        <v>英文版Q&amp;A「Work Permit for foreign professionals」含Q1，說明兩法之主要差異及適用情形。英文翻譯清晰。</v>
       </c>
       <c r="E41" t="str">
         <v>每半年</v>
@@ -1227,10 +1227,10 @@
         <v>https://foreigntalentact.ndc.gov.tw/en/Content_List.aspx?n=6D379FB78830B556</v>
       </c>
       <c r="C42" t="str">
-        <v>【建議檢視】建議檢視法規內容是否導向最新版本（含115年1月1日施行之條文）。</v>
+        <v>【建議確認】英文版Q1列出monthly salary門檻（NT$47,971），建議確認金額是否為最新標準。另employer qualifications及foreign language teacher qualifications應確認與現行審查標準之英文版一致。</v>
       </c>
       <c r="D42" t="str">
-        <v>頁面說明法規內容，建議確認相關連結皆已更新至最新修法版本。</v>
+        <v>英文版Q&amp;A「Tutorial School Teachers」含多則問答，詳列foreign employee qualifications（monthly salary NT$47,971、international teaching experience等）、employer qualifications及foreign language teacher資格。內容詳盡。</v>
       </c>
       <c r="E42" t="str">
         <v>每半年</v>
@@ -1247,10 +1247,10 @@
         <v>https://foreigntalentact.ndc.gov.tw/en/Content_List.aspx?n=A6348643802C2013</v>
       </c>
       <c r="C43" t="str">
-        <v>【建議檢視】建議檢視法規內容是否導向最新版本（含115年1月1日施行之條文）。</v>
+        <v>【注意】英文版Q1提供之連結 https://www.awpft.moe.gov.tw/ 在先前連結檢查中回傳連線逾時，建議確認該Ministry of Education系統是否已更換網址，並更新英文版頁面連結。</v>
       </c>
       <c r="D43" t="str">
-        <v>頁面說明法規內容，建議確認相關連結皆已更新至最新修法版本。</v>
+        <v>英文版Q&amp;A「Foreign Teachers」含Q1（How to apply），說明依「Regulations Governing Employment Permits」向Ministry of Education申請，並附申請流程圖。外部連結awpft.moe.gov.tw疑似失效。</v>
       </c>
       <c r="E43" t="str">
         <v>每半年</v>
@@ -1267,10 +1267,10 @@
         <v>https://foreigntalentact.ndc.gov.tw/en/Content_List.aspx?n=C8A9CE44A503629E</v>
       </c>
       <c r="C44" t="str">
-        <v>【建議檢視】建議檢視法規內容是否導向最新版本（含115年1月1日施行之條文）。</v>
+        <v>【注意】1.英文版Q&amp;A中之連結 awpft.moe.gov.tw 疑似失效，建議確認並更新。2.附有1份PDF檔案，建議確認是否為115年修法後之最新英文版本。</v>
       </c>
       <c r="D44" t="str">
-        <v>頁面說明法規內容，建議確認相關連結皆已更新至最新修法版本。</v>
+        <v>英文版Q&amp;A「Experimental Education Staff」含多則問答，說明employment permit application system（awpft.moe.gov.tw）、permit period（up to 3 years）、fee（NT$500）等。附1份PDF。awpft.moe.gov.tw連結疑似失效。</v>
       </c>
       <c r="E44" t="str">
         <v>每半年</v>
@@ -1287,10 +1287,10 @@
         <v>https://foreigntalentact.ndc.gov.tw/en/Content_List.aspx?n=27D45BC5A758EF7D</v>
       </c>
       <c r="C45" t="str">
-        <v>【建議檢視】建議檢視法規內容是否導向最新版本（含115年1月1日施行之條文）。</v>
+        <v>【建議確認】英文版Q1指向Ministry of Education網站查詢top 1,500 universities名單，Q2列舉specialized/technical work types。建議確認教育部英文版連結是否有效且為最新名單。</v>
       </c>
       <c r="D45" t="str">
-        <v>頁面說明法規內容，建議確認相關連結皆已更新至最新修法版本。</v>
+        <v>英文版Q&amp;A「Individuals with Masters Degrees and graduates from top 1,500 universities」含多則問答，說明名單由Ministry of Education公告，並列舉specialized work types（construction, transportation, finance等）。</v>
       </c>
       <c r="E45" t="str">
         <v>每年</v>
@@ -1307,10 +1307,10 @@
         <v>https://foreigntalentact.ndc.gov.tw/en/Content_List.aspx?n=01E6DB369BA6DF71</v>
       </c>
       <c r="C46" t="str">
-        <v>【建議檢視】建議檢視法規內容是否導向最新版本（含115年1月1日施行之條文）。</v>
+        <v>【建議確認】英文版Q1說明exemption from work permit之情形（government consultants、university lectures、permanent residents等），建議確認是否需補充115年修法新增之免許可情形。</v>
       </c>
       <c r="D46" t="str">
-        <v>頁面說明法規內容，建議確認相關連結皆已更新至最新修法版本。</v>
+        <v>英文版Q&amp;A「Exemptions from work permit requirement」含Q1，說明government-hired consultants、university lecturers及permanent residents等免申請工作許可之情形。內容簡潔。</v>
       </c>
       <c r="E46" t="str">
         <v>每半年</v>
@@ -1327,10 +1327,10 @@
         <v>https://foreigntalentact.ndc.gov.tw/en/Content_List.aspx?n=4EA351CC703CADA7</v>
       </c>
       <c r="C47" t="str">
-        <v>【建議檢視】建議檢視法規內容是否導向最新版本（含115年1月1日施行之條文）。</v>
+        <v>【建議確認】英文版Q1定義Foreign Specialist Professional涵蓋12大領域，Q2說明application channels。建議確認英文版領域名稱是否與115年修法版本一致（是否含Environmental protection及Biotechnology）。</v>
       </c>
       <c r="D47" t="str">
-        <v>頁面說明法規內容，建議確認相關連結皆已更新至最新修法版本。</v>
+        <v>英文版Q&amp;A「Work permit for foreign special professionals」含Q1（definition: 12 fields）及Q2（application channels），英文翻譯清晰。</v>
       </c>
       <c r="E47" t="str">
         <v>每半年</v>
@@ -1347,10 +1347,10 @@
         <v>https://foreigntalentact.ndc.gov.tw/en/Content_List.aspx?n=AC68F9FBABA3F294</v>
       </c>
       <c r="C48" t="str">
-        <v>【建議檢視】建議檢視法規內容是否導向最新版本（含115年1月1日施行之條文）。</v>
+        <v>【建議修正】1.英文版附PDF檔案，建議確認是否為2021年版本（如是，需更新）。2.NIA platform連結（coa.immigration.gov.tw）應確認英文版有效性。3.建議確認Q&amp;A是否已涵蓋115年修法對Employment Gold Card validity period調整之說明。</v>
       </c>
       <c r="D48" t="str">
-        <v>頁面說明法規內容，建議確認相關連結皆已更新至最新修法版本。</v>
+        <v>英文版Q&amp;A「Employment Gold Card」含多則問答（application method、passport verification、extension、passport renewal等），連結至NIA「Foreign Professionals Online Application Platform」。附1份PDF。</v>
       </c>
       <c r="E48" t="str">
         <v>每季</v>
@@ -1367,10 +1367,10 @@
         <v>https://foreigntalentact.ndc.gov.tw/en/Content_List.aspx?n=142286B325EC8807</v>
       </c>
       <c r="C49" t="str">
-        <v>【建議檢視】建議檢視法規內容是否導向最新版本（含115年1月1日施行之條文）。</v>
+        <v>【建議確認】英文版Q&amp;A以表格呈現2類artistic work（performing &amp; visual arts、broadcasting &amp; publishing arts）之qualification criteria，建議確認英文版資格條件翻譯是否與現行管理辦法英文版一致。</v>
       </c>
       <c r="D49" t="str">
-        <v>頁面說明法規內容，建議確認相關連結皆已更新至最新修法版本。</v>
+        <v>英文版Q&amp;A「Foreign professionals engaged in artistic work」含多則問答，以表格說明2 types of artistic work之application channels及qualification requirements（international awards、work experience等）。</v>
       </c>
       <c r="E49" t="str">
         <v>每半年</v>
@@ -1387,10 +1387,10 @@
         <v>https://foreigntalentact.ndc.gov.tw/en/Content_List.aspx?n=B1F5BD91A6CC5AF7</v>
       </c>
       <c r="C50" t="str">
-        <v>【建議檢視】建議檢視法規內容是否導向最新版本（含115年1月1日施行之條文）。</v>
+        <v>【建議定期確認】英文版Q1指向Ministry of Education公告之top 200 universities名單，Q2說明permit period最長2年且不得延期。建議確認教育部英文版連結是否為最新年度名單。</v>
       </c>
       <c r="D50" t="str">
-        <v>頁面說明法規內容，建議確認相關連結皆已更新至最新修法版本。</v>
+        <v>英文版Q&amp;A「Individual work permits for graduates from top 200 universities」含多則問答，說明最近5年取得bachelor's degree or higher from top 200 universities者得申請individual work permit。</v>
       </c>
       <c r="E50" t="str">
         <v>每年</v>
@@ -1407,10 +1407,10 @@
         <v>https://foreigntalentact.ndc.gov.tw/en/Content_List.aspx?n=E5D6AE5344888855</v>
       </c>
       <c r="C51" t="str">
-        <v>【建議檢視】建議檢視法規內容是否導向最新版本（含115年1月1日施行之條文）。</v>
+        <v>【建議確認】英文版Q1引用Article 12說明overseas Chinese and foreign students取得associate degree後延期居留期間免工作許可。建議確認英文版條號引用是否為115年修法版本。</v>
       </c>
       <c r="D51" t="str">
-        <v>頁面說明法規內容，建議確認相關連結皆已更新至最新修法版本。</v>
+        <v>英文版Q&amp;A「Overseas Chinese and foreign students exempt from work permit」含Q1，說明依Article 12取得associate degree or higher之應屆畢業生延期居留期間從事work免申請permit。</v>
       </c>
       <c r="E51" t="str">
         <v>每半年</v>
@@ -1427,10 +1427,10 @@
         <v>https://foreigntalentact.ndc.gov.tw/en/Content_List.aspx?n=F4B9BE10B401E018</v>
       </c>
       <c r="C52" t="str">
-        <v>【建議檢視】建議檢視法規內容是否導向最新版本（含115年1月1日施行之條文）。</v>
+        <v>【建議確認】英文版Q2列出3項申請條件（monthly salary NT$47,971、graduated within 1 year、QS top 500），建議確認金額及條件是否與115年修法後之規定一致。另BOCA連結（boca.gov.tw）應確認英文版有效性。</v>
       </c>
       <c r="D52" t="str">
-        <v>頁面說明法規內容，建議確認相關連結皆已更新至最新修法版本。</v>
+        <v>英文版Q&amp;A「Employment-Seeking Visa」含Q1（definition: 3-month validity、maximum 6-month stay）及Q2（3 application conditions），連結至BOCA英文版頁面。</v>
       </c>
       <c r="E52" t="str">
         <v>每半年</v>
@@ -1447,10 +1447,10 @@
         <v>https://foreigntalentact.ndc.gov.tw/en/Content_List.aspx?n=577532E67D4448BB</v>
       </c>
       <c r="C53" t="str">
-        <v>【建議檢視】建議檢視法規內容是否導向最新版本（含115年1月1日施行之條文）。</v>
+        <v>【建議確認】英文版Q&amp;A說明Digital Nomad Visa之定義、申請條件（visa-exempt countries、annual income等）及停留期間（maximum 2 years），建議確認內容是否完整反映115年修法規定，特別是spouse and children之申請資格。另BOCA連結應確認英文版有效性。</v>
       </c>
       <c r="D53" t="str">
-        <v>頁面說明法規內容，建議確認相關連結皆已更新至最新修法版本。</v>
+        <v>英文版Q&amp;A「Digital Nomad Visa」含Q1（definition）及Q2（application conditions: visa-exempt countries、annual income threshold等），說明maximum total stay of 2 years。連結至BOCA英文版。已反映115年修法之2-year規定。</v>
       </c>
       <c r="E53" t="str">
         <v>每半年</v>
@@ -1467,10 +1467,10 @@
         <v>https://foreigntalentact.ndc.gov.tw/en/Content_List.aspx?n=27A5BB9474905080</v>
       </c>
       <c r="C54" t="str">
-        <v>【建議檢視】建議檢視法規內容是否導向最新版本（含115年1月1日施行之條文）。</v>
+        <v>【建議確認】英文版Q&amp;A引用Article 15及Article 32說明adult children之個人工作許可規定，外部連結指向Ministry of Labor服務網。建議確認條號引用是否為115年修法版本，並檢視英文翻譯準確性。</v>
       </c>
       <c r="D54" t="str">
-        <v>頁面說明法規內容，建議確認相關連結皆已更新至最新修法版本。</v>
+        <v>英文版Q&amp;A「Adult children of foreign professionals」含多則問答，說明取得permanent residence或naturalization之外國專業人才，其adult children符合residence條件者得申請individual work permit。</v>
       </c>
       <c r="E54" t="str">
         <v>每半年</v>
@@ -1487,10 +1487,10 @@
         <v>https://foreigntalentact.ndc.gov.tw/en/Content_List.aspx?n=E216AB320D1BDFF5</v>
       </c>
       <c r="C55" t="str">
-        <v>【建議檢視】建議檢視法規內容是否導向最新版本（含115年1月1日施行之條文）。</v>
+        <v>【建議確認】英文版Q&amp;A引用Article 15及Article 32說明spouse之工作許可規定（限foreign specialist professionals及foreign senior professionals之配偶），建議確認條號是否為115年修法版本，並檢視required documents清單之英文翻譯。</v>
       </c>
       <c r="D55" t="str">
-        <v>頁面說明法規內容，建議確認相關連結皆已更新至最新修法版本。</v>
+        <v>英文版Q&amp;A「Work regulations for spouses」含Q1（regulations）及Q2（required documents），說明foreign specialist/senior professionals之spouses經permitted dependent residence者得申請work permit。</v>
       </c>
       <c r="E55" t="str">
         <v>每半年</v>
@@ -1507,10 +1507,10 @@
         <v>https://foreigntalentact.ndc.gov.tw/en/Content_List.aspx?n=BC793035C243B445</v>
       </c>
       <c r="C56" t="str">
-        <v>【建議檢視】建議檢視法規內容是否導向最新版本（含115年1月1日施行之條文）。</v>
+        <v>【建議檢視】英文版Q&amp;A「Visa/Residency」目錄頁列出5個子項目，建議確認子項名稱英文翻譯是否一致。</v>
       </c>
       <c r="D56" t="str">
-        <v>頁面說明法規內容，建議確認相關連結皆已更新至最新修法版本。</v>
+        <v>英文版Q&amp;A「Visa/Residency」目錄頁列出Residence for Professionals and Family、Permanent Residence、Visitor Visa of Lineal Ascendants、Cancellation of Permanent Residence、Adult Children with Disability等5個子項。</v>
       </c>
       <c r="E56" t="str">
         <v>每半年</v>
@@ -1527,10 +1527,10 @@
         <v>https://foreigntalentact.ndc.gov.tw/en/Content_List.aspx?n=2DE00EDE9CB5B796</v>
       </c>
       <c r="C57" t="str">
-        <v>【建議檢視】建議檢視法規內容是否導向最新版本（含115年1月1日施行之條文）。</v>
+        <v>【建議確認】英文版Q&amp;A詳列Gold Card持有者之foreign family申請ARC所需文件（passport、proof of relationship、photos、ARC fee等），建議確認：(1)ARC fee金額是否為最新；(2)NIA連結（immigration.gov.tw）英文版是否有效。</v>
       </c>
       <c r="D57" t="str">
-        <v>頁面說明法規內容，建議確認相關連結皆已更新至最新修法版本。</v>
+        <v>英文版Q&amp;A「Residence for Foreign Professionals and Family」含多則問答，詳列Gold Card持有者家屬之ARC申請文件及費用。外部連結指向NIA相關英文頁面。</v>
       </c>
       <c r="E57" t="str">
         <v>每半年</v>
@@ -1547,10 +1547,10 @@
         <v>https://foreigntalentact.ndc.gov.tw/en/Content_List.aspx?n=A2224A7A67D9DEEA</v>
       </c>
       <c r="C58" t="str">
-        <v>【建議檢視】建議檢視法規內容是否導向最新版本（含115年1月1日施行之條文）。</v>
+        <v>【建議確認】英文版Q&amp;A說明Gold Card持有者申請APRC之條件（3 years、average 183 days/year等），建議確認：(1)條件是否已反映115年修法版本；(2)英文版是否需補充non-Gold Card holders之permanent residence說明。</v>
       </c>
       <c r="D58" t="str">
-        <v>頁面說明法規內容，建議確認相關連結皆已更新至最新修法版本。</v>
+        <v>英文版Q&amp;A「Permanent Residence」含多則問答，說明Gold Card持有者需滿3 years、average 183 days/year居住、good conduct、no criminal record等條件。Q2另說明non-Gold Card之specialist professionals申請年限。</v>
       </c>
       <c r="E58" t="str">
         <v>每半年</v>
@@ -1567,10 +1567,10 @@
         <v>https://foreigntalentact.ndc.gov.tw/en/Content_List.aspx?n=5C3EE7E5E1BAB617</v>
       </c>
       <c r="C59" t="str">
-        <v>【建議檢視】建議檢視法規內容是否導向最新版本（含115年1月1日施行之條文）。</v>
+        <v>【建議確認】英文版Q&amp;A說明lineal ascendants（parents/grandparents）之visitor visa申請方式及所需文件，外部連結指向BOCA英文版。建議確認：(1)BOCA連結有效性；(2)停留期間（maximum 1 year、extension without exit）之英文說明是否完整。</v>
       </c>
       <c r="D59" t="str">
-        <v>頁面說明法規內容，建議確認相關連結皆已更新至最新修法版本。</v>
+        <v>英文版Q&amp;A「Visitor Visa of Lineal Ascendants」含多則問答，說明foreign specialist/senior professionals之lineal ascendants申請visitor visa之flow、documents及fees。外部連結指向BOCA英文版。</v>
       </c>
       <c r="E59" t="str">
         <v>每半年</v>
@@ -1587,10 +1587,10 @@
         <v>https://foreigntalentact.ndc.gov.tw/en/Content_List.aspx?n=A3F4CFF03E67E8D0</v>
       </c>
       <c r="C60" t="str">
-        <v>【建議檢視】建議檢視法規內容是否導向最新版本（含115年1月1日施行之條文）。</v>
+        <v>【建議確認】英文版Q1說明「abroad for over 5 years without entering Taiwan」將被revoke APRC，建議確認此為115年修法第21條規定，並確認英文翻譯是否準確（revoked vs. repealed用語一致性）。</v>
       </c>
       <c r="D60" t="str">
-        <v>頁面說明法規內容，建議確認相關連結皆已更新至最新修法版本。</v>
+        <v>英文版Q&amp;A「Cancellation of Permanent Residence」僅Q1一則，說明持有APRC但出國超過5年未入境者將被revoke permanent resident permit並註銷APRC。</v>
       </c>
       <c r="E60" t="str">
         <v>每半年</v>
@@ -1607,10 +1607,10 @@
         <v>https://foreigntalentact.ndc.gov.tw/en/Content_List.aspx?n=5979498B145C9F2D</v>
       </c>
       <c r="C61" t="str">
-        <v>【建議檢視】建議檢視法規內容是否導向最新版本（含115年1月1日施行之條文）。</v>
+        <v>【建議確認】英文版Q&amp;A說明disability認定標準（Barthel Index 30 or below等），建議確認：(1)認定標準是否與115年修法後之規定一致；(2)英文翻譯之醫療術語是否準確。</v>
       </c>
       <c r="D61" t="str">
-        <v>頁面說明法規內容，建議確認相關連結皆已更新至最新修法版本。</v>
+        <v>英文版Q&amp;A「Adult Children with Disability」含Q1（required documents: certification from nationality country、Barthel Index 30 or below）及Q2（alternative when overseas certificate unavailable），說明具體認定標準及overseas verification要求。</v>
       </c>
       <c r="E61" t="str">
         <v>每半年</v>
@@ -1627,10 +1627,10 @@
         <v>https://foreigntalentact.ndc.gov.tw/en/Content_List.aspx?n=5454F27194671145</v>
       </c>
       <c r="C62" t="str">
-        <v>【建議檢視】建議檢視法規內容是否導向最新版本（含115年1月1日施行之條文）。</v>
+        <v>【建議檢視】英文版Q&amp;A「Benefits and Social Securities」目錄頁列出6個子項目。建議確認是否需因應115年修法新增英文版子項（如Article 28 disability care services、Article 29 long-term care等，定自2026年6月30日施行）。</v>
       </c>
       <c r="D62" t="str">
-        <v>頁面說明法規內容，建議確認相關連結皆已更新至最新修法版本。</v>
+        <v>英文版Q&amp;A「Benefits and Social Securities」目錄頁列出Tax Concession、National Health Insurance、New Labor Pension、Employment Insurance、Retirement of Teachers、Science Park Teachers等6個子項。</v>
       </c>
       <c r="E62" t="str">
         <v>每半年</v>
@@ -1647,10 +1647,10 @@
         <v>https://foreigntalentact.ndc.gov.tw/en/Content_List.aspx?n=885B4035CE9EAB3E</v>
       </c>
       <c r="C63" t="str">
-        <v>【建議檢視】建議檢視法規內容是否導向最新版本（含115年1月1日施行之條文）。</v>
+        <v>【建議確認】英文版Tax Concession Q&amp;A頁面附2份PDF檔案（Q&amp;A及Application Documents），建議確認：(1)PDF內容是否為115年修法後之最新英文版本；(2)Article條號引用是否已更新。</v>
       </c>
       <c r="D63" t="str">
-        <v>頁面說明法規內容，建議確認相關連結皆已更新至最新修法版本。</v>
+        <v>英文版Q&amp;A「Tax Concession」頁面僅顯示2份PDF附件（Tax Concession Q&amp;A.pdf及Application Documents.pdf），無直接顯示之問答內容。英文版以PDF提供完整Q&amp;A及申請文件說明。</v>
       </c>
       <c r="E63" t="str">
         <v>每年</v>
@@ -1667,10 +1667,10 @@
         <v>https://foreigntalentact.ndc.gov.tw/en/Content_List.aspx?n=9D9AEFDF9A45B299</v>
       </c>
       <c r="C64" t="str">
-        <v>【建議檢視】建議檢視法規內容是否導向最新版本（含115年1月1日施行之條文）。</v>
+        <v>【建議確認】英文版NHI Q&amp;A說明enrollment eligibility及免6-month waiting period規定，建議確認：(1)內容是否反映115年修法版本（Article 23）；(2)employer/self-employed身分之英文說明是否完整。</v>
       </c>
       <c r="D64" t="str">
-        <v>頁面說明法規內容，建議確認相關連結皆已更新至最新修法版本。</v>
+        <v>英文版Q&amp;A「National Health Insurance」含多則問答，說明NHI為compulsory social insurance、enrollment categories、exemption from 6-month waiting period及dependent enrollment。英文翻譯詳盡。</v>
       </c>
       <c r="E64" t="str">
         <v>每半年</v>
@@ -1687,10 +1687,10 @@
         <v>https://foreigntalentact.ndc.gov.tw/en/Content_List.aspx?n=C90F39DF3D38CA2C</v>
       </c>
       <c r="C65" t="str">
-        <v>【建議檢視】建議檢視法規內容是否導向最新版本（含115年1月1日施行之條文）。</v>
+        <v>【建議確認】英文版Labor Pension Q&amp;A附1份PDF，外部連結含Bureau of Labor Insurance e-service及website。建議確認：(1)英文版Q&amp;A是否已更新為115年修法版本（Article 24）；(2)PDF及外部連結英文版是否有效。</v>
       </c>
       <c r="D65" t="str">
-        <v>頁面說明法規內容，建議確認相關連結皆已更新至最新修法版本。</v>
+        <v>英文版Q&amp;A「New Labor Pension System」含多則問答，說明employer monthly contribution 6%、voluntary contribution 6%、implementation timeline及claiming methods。附1份PDF，外部連結至Bureau of Labor Insurance。</v>
       </c>
       <c r="E65" t="str">
         <v>每半年</v>
@@ -1707,10 +1707,10 @@
         <v>https://foreigntalentact.ndc.gov.tw/en/Content_List.aspx?n=97158A60837C8307</v>
       </c>
       <c r="C66" t="str">
-        <v>【建議檢視】建議檢視法規內容是否導向最新版本（含115年1月1日施行之條文）。</v>
+        <v>【建議確認】英文版Employment Insurance Q&amp;A明確引用「amended Article 25 effective January 1, 2025」，附1份PDF。建議確認PDF內容及Bureau of Labor Insurance連結是否為最新英文版本。</v>
       </c>
       <c r="D66" t="str">
-        <v>頁面說明法規內容，建議確認相關連結皆已更新至最新修法版本。</v>
+        <v>英文版Q&amp;A「Employment Insurance」含多則問答，明確引用Article 25（amended, effective January 1, 2025），說明permanent residents為Employment Insurance Act適用對象。附1份PDF。已反映115年修法。</v>
       </c>
       <c r="E66" t="str">
         <v>每半年</v>
@@ -1727,10 +1727,10 @@
         <v>https://foreigntalentact.ndc.gov.tw/en/Content_List.aspx?n=B412A0AF89B19A9D</v>
       </c>
       <c r="C67" t="str">
-        <v>【建議檢視】建議檢視法規內容是否導向最新版本（含115年1月1日施行之條文）。</v>
+        <v>【建議確認】英文版Q1引用Article 26說明外國教師退休規定，建議確認英文版條號引用是否為115年修法版本，並確認「Act Governing the Retirement of Public School Teachers」之英文翻譯是否為官方用語。</v>
       </c>
       <c r="D67" t="str">
-        <v>頁面說明法規內容，建議確認相關連結皆已更新至最新修法版本。</v>
+        <v>英文版Q&amp;A「Retirement of Foreign Teachers」含Q1，說明外國專業人才擔任public school teachers、government research personnel之退休事項applicable to相關條例，permanent residents得選擇lump-sum或monthly pension。</v>
       </c>
       <c r="E67" t="str">
         <v>每半年</v>
@@ -1747,10 +1747,10 @@
         <v>https://foreigntalentact.ndc.gov.tw/en/Content_List.aspx?n=77C9A2195D46E1A9</v>
       </c>
       <c r="C68" t="str">
-        <v>【建議檢視】建議檢視法規內容是否導向最新版本（含115年1月1日施行之條文）。</v>
+        <v>【建議確認】英文版Q1引用Article 27（115年新增條文）說明Science Park bilingual department教師退休保障，建議確認英文翻譯是否準確，此為新增條文應確保內容正確。</v>
       </c>
       <c r="D68" t="str">
-        <v>頁面說明法規內容，建議確認相關連結皆已更新至最新修法版本。</v>
+        <v>英文版Q&amp;A「Retirement guarantees for teachers in bilingual departments of schools in Science Parks」含Q1，確認外國教師在retirement、severance、survivor's benefits等事項上applicable to public school teacher regulations。此為115年修法新增Article 27。</v>
       </c>
       <c r="E68" t="str">
         <v>每半年</v>
@@ -1767,10 +1767,10 @@
         <v>https://foreigntalentact.ndc.gov.tw/en/Content_List.aspx?n=BB03D278AB19EE3E</v>
       </c>
       <c r="C69" t="str">
-        <v>【建議定期更新】建議每月/季更新統計數據，並確認圖表或附件是否為最新月份。</v>
+        <v>【建議定期更新】英文版Statistics頁面以Employment Gold Card monthly statistics為主，最新資料為2026年1月。建議：(1)每月發布英文版最新統計；(2)考慮增加其他指標之英文版統計資料。</v>
       </c>
       <c r="D69" t="str">
-        <v>頁面提供歷年統計數據，建議持續更新以反映最新人才延攬成效。</v>
+        <v>英文版Statistics頁面列出2018年至2026年各月之Employment Gold Card Statistics，按年度分類。最新資料為2026年1月，更新頻率約每月一次。統計內容僅涵蓋Employment Gold Card。</v>
       </c>
       <c r="E69" t="str">
         <v>每月</v>
@@ -1787,10 +1787,10 @@
         <v>https://foreigntalentact.ndc.gov.tw/en/cp.aspx?n=D927ED39BDAE7478&amp;s=DA2F7BC919B77E24</v>
       </c>
       <c r="C70" t="str">
-        <v>【建議檢視】建議檢視法規內容是否導向最新版本（含115年1月1日施行之條文）。</v>
+        <v>【建議確認】英文版Contact頁面導引至Contact TAIWAN website（talent.nat.gov.tw），建議確認：(1)英文版Talent Taiwan連結是否有效；(2)是否需增列各主管機關之英文聯絡方式（如NIA service hotline等）。</v>
       </c>
       <c r="D70" t="str">
-        <v>頁面說明法規內容，建議確認相關連結皆已更新至最新修法版本。</v>
+        <v>英文版Contact頁面引導使用者至Contact TAIWAN website查看work permits、visas、ARCs等申辦資訊，並提供「Contact Us」留言管道。未直接列出電話或email。</v>
       </c>
       <c r="E70" t="str">
         <v>每半年</v>
@@ -1807,10 +1807,10 @@
         <v>https://foreigntalentact.ndc.gov.tw/en/SiteMap.aspx?n=CA3FB4291106E1D9 "Sitemap"</v>
       </c>
       <c r="C71" t="str">
-        <v>【建議檢視】建議檢視頁面內文及外部連結有效性，並確認是否符合2025修法後之最新規定。</v>
+        <v>【建議檢視】英文版Sitemap頁面列出無障礙設計說明及快速鍵設定，並提供完整英文版站內架構。建議於網站架構變更時同步更新英文版Sitemap。</v>
       </c>
       <c r="D71" t="str">
-        <v>已檢視頁面排版與連結。建議持續追蹤修法後相關資訊之更新情形。</v>
+        <v>英文版Sitemap頁面說明accessibility design principles及keyboard shortcuts（Alt+U/C/L/Z），以樹狀結構列出完整英文版網站架構（含所有子頁連結）。</v>
       </c>
       <c r="E71" t="str">
         <v>每半年</v>
